--- a/analysis/flume_tank_2026/data/flume_tank_data_2026.xlsx
+++ b/analysis/flume_tank_2026/data/flume_tank_data_2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="87">
   <si>
     <t>trial</t>
   </si>
@@ -101,10 +101,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>PNE</t>
-  </si>
-  <si>
-    <t>1.2a</t>
+    <t>PNE (2026)</t>
   </si>
   <si>
     <t>EBS</t>
@@ -114,9 +111,6 @@
   </si>
   <si>
     <t>B</t>
-  </si>
-  <si>
-    <t>1.2b</t>
   </si>
   <si>
     <t>Rig B; 20" setback in the top, 10" in the middle, 20" bottom</t>
@@ -131,7 +125,7 @@
     <t>D</t>
   </si>
   <si>
-    <t>RACE</t>
+    <t>RACE (2026)</t>
   </si>
   <si>
     <t>GOA</t>
@@ -185,7 +179,7 @@
     <t>J</t>
   </si>
   <si>
-    <t>Standard</t>
+    <t>standard</t>
   </si>
   <si>
     <t>Rig J; 180' bridles, standard setback 18" top, 6" top; 0" footrope; middle bridle touching the bottom similar to the current PNE; no added weight on the bridles</t>
@@ -266,10 +260,16 @@
     <t>bottom_setback_links</t>
   </si>
   <si>
+    <t>PNE</t>
+  </si>
+  <si>
     <t>Rig A; Rigging prior to adjusting setback; height coming in low; 1 link middle (2.5"); 20" bottom setback</t>
   </si>
   <si>
     <t>Rig C; 20" setback in the top, 10" in the middle, 20" bottom; truncated bridles (sweeps 75 cm)</t>
+  </si>
+  <si>
+    <t>RACE</t>
   </si>
   <si>
     <t>Rig J; 180' bridles, standard setback 18" top, 6" middle; 0" footrope; middle bridle touching the bottom similar to the current PNE; no added weight on the bridles</t>
@@ -361,6 +361,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -370,9 +373,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -491,7 +491,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D20:J23" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D24:J27" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -808,14 +808,14 @@
       <c r="C2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>30</v>
+      <c r="D2" s="4">
+        <v>1.2</v>
       </c>
       <c r="E2" s="4">
         <v>27.9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" s="5">
         <v>35.0</v>
@@ -881,7 +881,7 @@
         <v>22.6</v>
       </c>
       <c r="AB2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -889,19 +889,19 @@
         <v>0.0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>34</v>
+      <c r="D3" s="4">
+        <v>1.2</v>
       </c>
       <c r="E3" s="4">
         <v>27.9</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="5">
         <v>35.0</v>
@@ -967,7 +967,7 @@
         <v>22.8</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -975,19 +975,19 @@
         <v>1.0</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>34</v>
+      <c r="D4" s="4">
+        <v>1.2</v>
       </c>
       <c r="E4" s="7">
         <v>27.9</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G4" s="5">
         <v>35.0</v>
@@ -1058,19 +1058,19 @@
         <v>2.0</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>34</v>
+      <c r="D5" s="4">
+        <v>1.2</v>
       </c>
       <c r="E5" s="5">
         <v>27.9</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="5">
         <v>35.0</v>
@@ -1142,19 +1142,19 @@
         <v>3.0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
+      <c r="D6" s="4">
+        <v>1.2</v>
       </c>
       <c r="E6" s="5">
         <v>27.9</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="5">
         <v>35.0</v>
@@ -1226,19 +1226,19 @@
         <v>4.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>34</v>
+      <c r="D7" s="4">
+        <v>1.2</v>
       </c>
       <c r="E7" s="5">
         <v>27.9</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="5">
         <v>35.0</v>
@@ -1310,19 +1310,19 @@
         <v>5.0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>34</v>
+      <c r="D8" s="4">
+        <v>1.2</v>
       </c>
       <c r="E8" s="5">
         <v>27.9</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G8" s="5">
         <v>35.0</v>
@@ -1394,19 +1394,19 @@
         <v>6.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
+      <c r="D9" s="4">
+        <v>1.2</v>
       </c>
       <c r="E9" s="5">
         <v>27.9</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="5">
         <v>35.0</v>
@@ -1478,19 +1478,19 @@
         <v>7.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>34</v>
+      <c r="D10" s="4">
+        <v>1.2</v>
       </c>
       <c r="E10" s="5">
         <v>27.9</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G10" s="5">
         <v>35.0</v>
@@ -1562,19 +1562,19 @@
         <v>8.0</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>34</v>
+      <c r="D11" s="4">
+        <v>1.2</v>
       </c>
       <c r="E11" s="5">
         <v>27.9</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G11" s="5">
         <v>35.0</v>
@@ -1646,19 +1646,19 @@
         <v>9.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>34</v>
+      <c r="D12" s="4">
+        <v>1.2</v>
       </c>
       <c r="E12" s="5">
         <v>27.9</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G12" s="5">
         <v>35.0</v>
@@ -1724,7 +1724,7 @@
         <v>30.5</v>
       </c>
       <c r="AB12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -1732,19 +1732,19 @@
         <v>10.0</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>34</v>
+      <c r="D13" s="4">
+        <v>1.2</v>
       </c>
       <c r="E13" s="5">
         <v>27.9</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G13" s="5">
         <v>35.0</v>
@@ -1816,19 +1816,19 @@
         <v>11.0</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>34</v>
+      <c r="D14" s="4">
+        <v>1.2</v>
       </c>
       <c r="E14" s="5">
         <v>27.9</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G14" s="5">
         <v>35.0</v>
@@ -1900,19 +1900,19 @@
         <v>12.0</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>34</v>
+      <c r="D15" s="4">
+        <v>1.2</v>
       </c>
       <c r="E15" s="5">
         <v>27.9</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G15" s="5">
         <v>35.0</v>
@@ -1984,19 +1984,19 @@
         <v>13.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>34</v>
+      <c r="D16" s="4">
+        <v>1.2</v>
       </c>
       <c r="E16" s="5">
         <v>27.9</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G16" s="5">
         <v>35.0</v>
@@ -2068,19 +2068,19 @@
         <v>14.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>34</v>
+      <c r="D17" s="4">
+        <v>1.2</v>
       </c>
       <c r="E17" s="5">
         <v>27.9</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="5">
         <v>35.0</v>
@@ -2152,19 +2152,19 @@
         <v>15.0</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>34</v>
+      <c r="D18" s="4">
+        <v>1.2</v>
       </c>
       <c r="E18" s="5">
         <v>27.9</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G18" s="5">
         <v>35.0</v>
@@ -2236,19 +2236,19 @@
         <v>16.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>34</v>
+      <c r="D19" s="4">
+        <v>1.2</v>
       </c>
       <c r="E19" s="5">
         <v>27.9</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="5">
         <v>35.0</v>
@@ -2320,10 +2320,10 @@
         <v>17.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D20" s="4">
         <v>1.0</v>
@@ -2332,7 +2332,7 @@
         <v>27.4</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G20" s="5">
         <v>34.0</v>
@@ -2398,7 +2398,7 @@
         <v>39.9</v>
       </c>
       <c r="AB20" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -2406,10 +2406,10 @@
         <v>18.0</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D21" s="4">
         <v>1.0</v>
@@ -2418,7 +2418,7 @@
         <v>27.4</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G21" s="5">
         <v>34.0</v>
@@ -2484,7 +2484,7 @@
         <v>39.2</v>
       </c>
       <c r="AB21" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
@@ -2492,10 +2492,10 @@
         <v>19.0</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D22" s="4">
         <v>1.0</v>
@@ -2504,7 +2504,7 @@
         <v>27.4</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G22" s="5">
         <v>34.0</v>
@@ -2570,7 +2570,7 @@
         <v>39.1</v>
       </c>
       <c r="AB22" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -2578,10 +2578,10 @@
         <v>20.0</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D23" s="4">
         <v>1.0</v>
@@ -2590,7 +2590,7 @@
         <v>27.4</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G23" s="5">
         <v>34.0</v>
@@ -2656,7 +2656,7 @@
         <v>33.2</v>
       </c>
       <c r="AB23" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -2664,10 +2664,10 @@
         <v>21.0</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D24" s="4">
         <v>1.0</v>
@@ -2676,7 +2676,7 @@
         <v>27.4</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G24" s="5">
         <v>34.0</v>
@@ -2748,10 +2748,10 @@
         <v>22.0</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D25" s="4">
         <v>1.0</v>
@@ -2760,7 +2760,7 @@
         <v>27.4</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G25" s="5">
         <v>34.0</v>
@@ -2832,10 +2832,10 @@
         <v>23.0</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D26" s="4">
         <v>1.0</v>
@@ -2844,7 +2844,7 @@
         <v>27.4</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G26" s="5">
         <v>34.0</v>
@@ -2916,10 +2916,10 @@
         <v>24.0</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D27" s="4">
         <v>1.0</v>
@@ -2928,7 +2928,7 @@
         <v>27.4</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G27" s="5">
         <v>34.0</v>
@@ -3000,10 +3000,10 @@
         <v>25.0</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D28" s="4">
         <v>1.0</v>
@@ -3012,7 +3012,7 @@
         <v>27.4</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G28" s="5">
         <v>34.0</v>
@@ -3078,7 +3078,7 @@
         <v>26.4</v>
       </c>
       <c r="AB28" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
@@ -3086,10 +3086,10 @@
         <v>26.0</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D29" s="4">
         <v>1.0</v>
@@ -3098,7 +3098,7 @@
         <v>27.4</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G29" s="5">
         <v>34.0</v>
@@ -3170,10 +3170,10 @@
         <v>27.0</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="4">
         <v>1.0</v>
@@ -3182,7 +3182,7 @@
         <v>27.4</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G30" s="5">
         <v>34.0</v>
@@ -3253,10 +3253,10 @@
         <v>28.0</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D31" s="4">
         <v>1.0</v>
@@ -3265,7 +3265,7 @@
         <v>27.4</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G31" s="5">
         <v>34.0</v>
@@ -3337,10 +3337,10 @@
         <v>29.0</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D32" s="4">
         <v>1.0</v>
@@ -3349,7 +3349,7 @@
         <v>27.4</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G32" s="5">
         <v>34.0</v>
@@ -3421,10 +3421,10 @@
         <v>30.0</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D33" s="4">
         <v>1.0</v>
@@ -3433,7 +3433,7 @@
         <v>27.4</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G33" s="5">
         <v>34.0</v>
@@ -3505,10 +3505,10 @@
         <v>31.0</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D34" s="4">
         <v>1.0</v>
@@ -3517,7 +3517,7 @@
         <v>27.4</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G34" s="5">
         <v>34.0</v>
@@ -3589,10 +3589,10 @@
         <v>32.0</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D35" s="4">
         <v>1.0</v>
@@ -3601,7 +3601,7 @@
         <v>27.4</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G35" s="5">
         <v>34.0</v>
@@ -3673,10 +3673,10 @@
         <v>33.0</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D36" s="4">
         <v>1.0</v>
@@ -3685,7 +3685,7 @@
         <v>27.4</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G36" s="5">
         <v>34.0</v>
@@ -3751,7 +3751,7 @@
         <v>24.2</v>
       </c>
       <c r="AB36" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -3759,10 +3759,10 @@
         <v>34.0</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D37" s="4">
         <v>1.0</v>
@@ -3771,7 +3771,7 @@
         <v>27.4</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G37" s="5">
         <v>34.0</v>
@@ -3837,7 +3837,7 @@
         <v>18.9</v>
       </c>
       <c r="AB37" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
@@ -3845,10 +3845,10 @@
         <v>35.0</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D38" s="4">
         <v>1.0</v>
@@ -3857,7 +3857,7 @@
         <v>27.4</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G38" s="5">
         <v>34.0</v>
@@ -3929,10 +3929,10 @@
         <v>36.0</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D39" s="4">
         <v>1.0</v>
@@ -3941,7 +3941,7 @@
         <v>27.4</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G39" s="5">
         <v>34.0</v>
@@ -4007,7 +4007,7 @@
         <v>18.6</v>
       </c>
       <c r="AB39" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -4015,10 +4015,10 @@
         <v>37.0</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D40" s="4">
         <v>1.0</v>
@@ -4027,7 +4027,7 @@
         <v>27.4</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G40" s="5">
         <v>34.0</v>
@@ -4099,10 +4099,10 @@
         <v>38.0</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D41" s="4">
         <v>1.0</v>
@@ -4111,7 +4111,7 @@
         <v>27.4</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G41" s="5">
         <v>34.0</v>
@@ -4183,10 +4183,10 @@
         <v>39.0</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D42" s="4">
         <v>1.0</v>
@@ -4195,7 +4195,7 @@
         <v>27.4</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G42" s="5">
         <v>34.0</v>
@@ -4267,10 +4267,10 @@
         <v>40.0</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D43" s="4">
         <v>1.0</v>
@@ -4279,7 +4279,7 @@
         <v>27.4</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43" s="5">
         <v>34.0</v>
@@ -4351,10 +4351,10 @@
         <v>41.0</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D44" s="4">
         <v>1.0</v>
@@ -4363,7 +4363,7 @@
         <v>27.4</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G44" s="5">
         <v>34.0</v>
@@ -4435,10 +4435,10 @@
         <v>42.0</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D45" s="4">
         <v>1.0</v>
@@ -4447,7 +4447,7 @@
         <v>27.4</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" s="5">
         <v>34.0</v>
@@ -4513,7 +4513,7 @@
         <v>32.6</v>
       </c>
       <c r="AB45" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -4521,10 +4521,10 @@
         <v>43.0</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D46" s="4">
         <v>1.0</v>
@@ -4533,7 +4533,7 @@
         <v>27.4</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G46" s="5">
         <v>34.0</v>
@@ -4605,10 +4605,10 @@
         <v>44.0</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D47" s="4">
         <v>1.0</v>
@@ -4617,7 +4617,7 @@
         <v>27.4</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G47" s="5">
         <v>34.0</v>
@@ -4689,10 +4689,10 @@
         <v>45.0</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D48" s="4">
         <v>1.0</v>
@@ -4701,7 +4701,7 @@
         <v>27.4</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G48" s="5">
         <v>34.0</v>
@@ -4773,10 +4773,10 @@
         <v>46.0</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D49" s="4">
         <v>1.0</v>
@@ -4785,7 +4785,7 @@
         <v>27.4</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G49" s="5">
         <v>34.0</v>
@@ -4857,19 +4857,19 @@
         <v>47.0</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1.2</v>
       </c>
       <c r="E50" s="5">
         <v>27.8</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G50" s="5">
         <v>34.0</v>
@@ -4935,7 +4935,7 @@
         <v>26.8</v>
       </c>
       <c r="AB50" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -4943,19 +4943,19 @@
         <v>48.0</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1.2</v>
       </c>
       <c r="E51" s="5">
         <v>27.8</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G51" s="5">
         <v>34.0</v>
@@ -5021,7 +5021,7 @@
         <v>26.1</v>
       </c>
       <c r="AB51" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -5029,19 +5029,19 @@
         <v>49.0</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1.2</v>
       </c>
       <c r="E52" s="5">
         <v>27.8</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" s="5">
         <v>34.0</v>
@@ -5107,7 +5107,7 @@
         <v>25.6</v>
       </c>
       <c r="AB52" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -5115,19 +5115,19 @@
         <v>50.0</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D53" s="4">
+        <v>1.2</v>
       </c>
       <c r="E53" s="5">
         <v>27.8</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G53" s="5">
         <v>34.0</v>
@@ -5193,7 +5193,7 @@
         <v>30.5</v>
       </c>
       <c r="AB53" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -5201,19 +5201,19 @@
         <v>51.0</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D54" s="4">
+        <v>1.2</v>
       </c>
       <c r="E54" s="5">
         <v>27.8</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G54" s="5">
         <v>34.0</v>
@@ -5279,7 +5279,7 @@
         <v>30.8</v>
       </c>
       <c r="AB54" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -5287,19 +5287,19 @@
         <v>52.0</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D55" s="4">
+        <v>1.2</v>
       </c>
       <c r="E55" s="5">
         <v>27.8</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G55" s="5">
         <v>34.0</v>
@@ -5365,7 +5365,7 @@
         <v>30.7</v>
       </c>
       <c r="AB55" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56">
@@ -5373,19 +5373,19 @@
         <v>53.0</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D56" s="4">
+        <v>1.2</v>
       </c>
       <c r="E56" s="5">
         <v>27.8</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G56" s="5">
         <v>34.0</v>
@@ -5451,7 +5451,7 @@
         <v>24.4</v>
       </c>
       <c r="AB56" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
@@ -5459,19 +5459,19 @@
         <v>54.0</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D57" s="4" t="s">
-        <v>34</v>
+      <c r="D57" s="4">
+        <v>1.2</v>
       </c>
       <c r="E57" s="5">
         <v>27.9</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G57" s="5">
         <v>35.0</v>
@@ -5537,7 +5537,7 @@
         <v>35.8</v>
       </c>
       <c r="AB57" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58">
@@ -5545,19 +5545,19 @@
         <v>55.0</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>34</v>
+      <c r="D58" s="4">
+        <v>1.2</v>
       </c>
       <c r="E58" s="5">
         <v>27.9</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G58" s="5">
         <v>35.0</v>
@@ -5629,19 +5629,19 @@
         <v>56.0</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>34</v>
+      <c r="D59" s="4">
+        <v>1.2</v>
       </c>
       <c r="E59" s="5">
         <v>27.9</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G59" s="5">
         <v>35.0</v>
@@ -5713,19 +5713,19 @@
         <v>57.0</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>34</v>
+      <c r="D60" s="4">
+        <v>1.2</v>
       </c>
       <c r="E60" s="5">
         <v>27.9</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G60" s="5">
         <v>35.0</v>
@@ -5797,19 +5797,19 @@
         <v>58.0</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>34</v>
+      <c r="D61" s="4">
+        <v>1.2</v>
       </c>
       <c r="E61" s="5">
         <v>27.9</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G61" s="5">
         <v>35.0</v>
@@ -5881,19 +5881,19 @@
         <v>59.0</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D62" s="4" t="s">
-        <v>34</v>
+      <c r="D62" s="4">
+        <v>1.2</v>
       </c>
       <c r="E62" s="5">
         <v>27.9</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G62" s="5">
         <v>35.0</v>
@@ -5965,19 +5965,19 @@
         <v>60.0</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D63" s="4" t="s">
-        <v>34</v>
+      <c r="D63" s="4">
+        <v>1.2</v>
       </c>
       <c r="E63" s="5">
         <v>27.9</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G63" s="5">
         <v>35.0</v>
@@ -6049,19 +6049,19 @@
         <v>61.0</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>34</v>
+      <c r="D64" s="4">
+        <v>1.2</v>
       </c>
       <c r="E64" s="5">
         <v>27.9</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G64" s="5">
         <v>35.0</v>
@@ -6133,19 +6133,19 @@
         <v>62.0</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>34</v>
+      <c r="D65" s="4">
+        <v>1.2</v>
       </c>
       <c r="E65" s="5">
         <v>27.9</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G65" s="5">
         <v>35.0</v>
@@ -6211,7 +6211,7 @@
         <v>22.4</v>
       </c>
       <c r="AB65" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66">
@@ -6219,19 +6219,19 @@
         <v>63.0</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>34</v>
+      <c r="D66" s="4">
+        <v>1.2</v>
       </c>
       <c r="E66" s="5">
         <v>27.9</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G66" s="5">
         <v>35.0</v>
@@ -6303,19 +6303,19 @@
         <v>64.0</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D67" s="4" t="s">
-        <v>34</v>
+      <c r="D67" s="4">
+        <v>1.2</v>
       </c>
       <c r="E67" s="5">
         <v>27.9</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G67" s="5">
         <v>35.0</v>
@@ -6387,19 +6387,19 @@
         <v>65.0</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>34</v>
+      <c r="D68" s="4">
+        <v>1.2</v>
       </c>
       <c r="E68" s="5">
         <v>27.9</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G68" s="5">
         <v>35.0</v>
@@ -6471,19 +6471,19 @@
         <v>66.0</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>34</v>
+      <c r="D69" s="4">
+        <v>1.2</v>
       </c>
       <c r="E69" s="5">
         <v>27.9</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G69" s="5">
         <v>35.0</v>
@@ -6555,19 +6555,19 @@
         <v>67.0</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>34</v>
+      <c r="D70" s="4">
+        <v>1.2</v>
       </c>
       <c r="E70" s="5">
         <v>27.9</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G70" s="5">
         <v>35.0</v>
@@ -6633,7 +6633,7 @@
         <v>17.6</v>
       </c>
       <c r="AB70" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71">
@@ -6641,19 +6641,19 @@
         <v>68.0</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>34</v>
+      <c r="D71" s="4">
+        <v>1.2</v>
       </c>
       <c r="E71" s="5">
         <v>27.9</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G71" s="5">
         <v>35.0</v>
@@ -6725,19 +6725,19 @@
         <v>69.0</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>34</v>
+      <c r="D72" s="4">
+        <v>1.2</v>
       </c>
       <c r="E72" s="5">
         <v>27.9</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G72" s="5">
         <v>35.0</v>
@@ -6809,19 +6809,19 @@
         <v>70.0</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>57</v>
+      <c r="D73" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E73" s="5">
         <v>27.9</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G73" s="5">
         <v>35.0</v>
@@ -6887,7 +6887,7 @@
         <v>22.7</v>
       </c>
       <c r="AB73" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74">
@@ -6895,19 +6895,19 @@
         <v>71.0</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>57</v>
+      <c r="D74" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E74" s="5">
         <v>28.0</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G74" s="5">
         <v>35.0</v>
@@ -6973,7 +6973,7 @@
         <v>22.8</v>
       </c>
       <c r="AB74" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75">
@@ -6981,19 +6981,19 @@
         <v>72.0</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>57</v>
+      <c r="D75" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E75" s="5">
         <v>28.0</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G75" s="5">
         <v>35.0</v>
@@ -7065,19 +7065,19 @@
         <v>73.0</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D76" s="4" t="s">
-        <v>57</v>
+      <c r="D76" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E76" s="5">
         <v>28.0</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G76" s="5">
         <v>35.0</v>
@@ -7149,19 +7149,19 @@
         <v>74.0</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E77" s="5">
         <v>28.0</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G77" s="5">
         <v>34.0</v>
@@ -7227,7 +7227,7 @@
         <v>24.4</v>
       </c>
       <c r="AB77" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78">
@@ -7235,19 +7235,19 @@
         <v>75.0</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E78" s="5">
         <v>28.0</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G78" s="5">
         <v>34.0</v>
@@ -7319,19 +7319,19 @@
         <v>76.0</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E79" s="5">
         <v>28.0</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G79" s="5">
         <v>34.0</v>
@@ -7397,7 +7397,7 @@
         <v>24.1</v>
       </c>
       <c r="AB79" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -7405,19 +7405,19 @@
         <v>77.0</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E80" s="5">
         <v>28.0</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G80" s="5">
         <v>34.0</v>
@@ -7475,7 +7475,7 @@
         <v>23.5</v>
       </c>
       <c r="AB80" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81">
@@ -7483,19 +7483,19 @@
         <v>78.0</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E81" s="5">
         <v>26.1</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G81" s="5">
         <v>34.0</v>
@@ -7559,19 +7559,19 @@
         <v>79.0</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E82" s="5">
         <v>28.0</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G82" s="5">
         <v>34.0</v>
@@ -7635,19 +7635,19 @@
         <v>80.0</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E83" s="5">
         <v>28.0</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G83" s="5">
         <v>34.0</v>
@@ -7711,19 +7711,19 @@
         <v>81.0</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E84" s="5">
         <v>28.0</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G84" s="5">
         <v>34.0</v>
@@ -7787,19 +7787,19 @@
         <v>82.0</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E85" s="5">
         <v>28.0</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G85" s="5">
         <v>34.0</v>
@@ -7863,19 +7863,19 @@
         <v>83.0</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>57</v>
+      <c r="D86" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E86" s="5">
         <v>26.1</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G86" s="5">
         <v>35.0</v>
@@ -7896,7 +7896,7 @@
       <c r="M86" s="4">
         <v>16.0</v>
       </c>
-      <c r="N86" s="9">
+      <c r="N86" s="10">
         <f t="shared" ref="N86:N87" si="19">2.01*8</f>
         <v>16.08</v>
       </c>
@@ -7909,7 +7909,7 @@
       <c r="Q86" s="6">
         <v>17.9</v>
       </c>
-      <c r="R86" s="9">
+      <c r="R86" s="10">
         <f>0.884*8</f>
         <v>7.072</v>
       </c>
@@ -7939,19 +7939,19 @@
         <v>84.0</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>57</v>
+      <c r="D87" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E87" s="5">
         <v>26.1</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G87" s="5">
         <v>35.0</v>
@@ -8015,19 +8015,19 @@
         <v>85.0</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>57</v>
+      <c r="D88" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E88" s="5">
         <v>26.1</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G88" s="5">
         <v>35.0</v>
@@ -8091,19 +8091,19 @@
         <v>86.0</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>57</v>
+      <c r="D89" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E89" s="5">
         <v>26.1</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G89" s="5">
         <v>35.0</v>
@@ -8167,19 +8167,19 @@
         <v>87.0</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D90" s="4" t="s">
-        <v>57</v>
+      <c r="D90" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E90" s="5">
         <v>26.1</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G90" s="5">
         <v>35.0</v>
@@ -8243,19 +8243,19 @@
         <v>88.0</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>57</v>
+      <c r="D91" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="E91" s="5">
         <v>26.1</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G91" s="5">
         <v>35.0</v>
@@ -8319,19 +8319,19 @@
         <v>89.0</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C92" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>34</v>
+      <c r="D92" s="4">
+        <v>1.2</v>
       </c>
       <c r="E92" s="5">
         <v>27.9</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G92" s="5">
         <v>47.0</v>
@@ -8397,7 +8397,7 @@
         <v>21.6</v>
       </c>
       <c r="AB92" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93">
@@ -8405,19 +8405,19 @@
         <v>90.0</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>34</v>
+      <c r="D93" s="4">
+        <v>1.2</v>
       </c>
       <c r="E93" s="5">
         <v>27.9</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G93" s="5">
         <v>47.0</v>
@@ -8483,7 +8483,7 @@
         <v>21.8</v>
       </c>
       <c r="AB93" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94">
@@ -8491,7 +8491,7 @@
         <v>91.0</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>29</v>
@@ -8503,7 +8503,7 @@
         <v>27.9</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G94" s="5">
         <v>47.0</v>
@@ -8569,7 +8569,7 @@
         <v>22.5</v>
       </c>
       <c r="AB94" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95">
@@ -8577,7 +8577,7 @@
         <v>92.0</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>29</v>
@@ -8585,17 +8585,17 @@
       <c r="D95" s="4">
         <v>2.0</v>
       </c>
-      <c r="E95" s="10">
+      <c r="E95" s="11">
         <v>27.9</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G95" s="11"/>
-      <c r="H95" s="11"/>
+        <v>38</v>
+      </c>
+      <c r="G95" s="12"/>
+      <c r="H95" s="12"/>
       <c r="I95" s="6"/>
-      <c r="J95" s="11"/>
-      <c r="K95" s="11"/>
+      <c r="J95" s="12"/>
+      <c r="K95" s="12"/>
       <c r="L95" s="4">
         <v>3.0</v>
       </c>
@@ -8606,24 +8606,24 @@
         <f>1.99*8</f>
         <v>15.92</v>
       </c>
-      <c r="O95" s="11"/>
-      <c r="P95" s="11"/>
+      <c r="O95" s="12"/>
+      <c r="P95" s="12"/>
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
         <f>0.593*8</f>
         <v>4.744</v>
       </c>
-      <c r="S95" s="11"/>
-      <c r="T95" s="11"/>
-      <c r="U95" s="11"/>
-      <c r="V95" s="11"/>
-      <c r="W95" s="11"/>
-      <c r="X95" s="11"/>
-      <c r="Y95" s="11"/>
-      <c r="Z95" s="11"/>
-      <c r="AA95" s="12"/>
+      <c r="S95" s="12"/>
+      <c r="T95" s="12"/>
+      <c r="U95" s="12"/>
+      <c r="V95" s="12"/>
+      <c r="W95" s="12"/>
+      <c r="X95" s="12"/>
+      <c r="Y95" s="12"/>
+      <c r="Z95" s="12"/>
+      <c r="AA95" s="13"/>
       <c r="AB95" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96">
@@ -8631,10 +8631,10 @@
         <v>93.0</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D96" s="4">
         <v>2.0</v>
@@ -8643,7 +8643,7 @@
         <v>27.9</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G96" s="5">
         <v>47.0</v>
@@ -8709,7 +8709,7 @@
         <v>21.8</v>
       </c>
       <c r="AB96" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97">
@@ -8717,10 +8717,10 @@
         <v>94.0</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D97" s="4">
         <v>2.0</v>
@@ -8729,7 +8729,7 @@
         <v>27.9</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G97" s="5">
         <v>47.0</v>
@@ -8795,7 +8795,7 @@
         <v>22.5</v>
       </c>
       <c r="AB97" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="98">
@@ -8803,10 +8803,10 @@
         <v>95.0</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D98" s="4">
         <v>1.0</v>
@@ -8815,7 +8815,7 @@
         <v>27.4</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G98" s="5">
         <v>47.0</v>
@@ -8881,7 +8881,7 @@
         <v>23.4</v>
       </c>
       <c r="AB98" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="99">
@@ -8889,10 +8889,10 @@
         <v>96.0</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D99" s="4">
         <v>1.0</v>
@@ -8901,7 +8901,7 @@
         <v>27.4</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G99" s="5">
         <v>47.0</v>
@@ -8967,7 +8967,7 @@
         <v>23.4</v>
       </c>
       <c r="AB99" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -8992,739 +8992,867 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="J1" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="C2" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F2" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G2" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="I2" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="13" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="13">
+      <c r="E3" s="9">
         <v>3.43</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F3" s="9">
         <v>3.43</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G3" s="9">
         <v>8.0</v>
       </c>
-      <c r="H2" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="I2" s="13">
+      <c r="H3" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="I3" s="9">
         <v>8.0</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J3" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F4" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G4" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="I4" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="G5" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="13" t="s">
+    <row r="6">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="13">
+      <c r="B6" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="9">
         <v>3.43</v>
       </c>
-      <c r="F3" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="G3" s="13">
+      <c r="F6" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="G6" s="9">
         <v>8.0</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H6" s="9">
         <v>4.0</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I6" s="9">
         <v>8.0</v>
       </c>
-      <c r="J3" s="13" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="s">
+      <c r="J6" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="F4" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="G4" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="H4" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="I4" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="J4" s="13" t="s">
+      <c r="B7" s="9" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="F5" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="F6" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="C7" s="14">
         <v>1.0</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="13">
+      <c r="D7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="9">
         <v>3.43</v>
       </c>
-      <c r="F7" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>48</v>
+      <c r="F7" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>39</v>
+      <c r="A8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="C8" s="14">
         <v>1.0</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="13">
+      <c r="D8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="9">
         <v>3.43</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F10" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="14">
+        <v>1.0</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F12" s="9">
         <v>1.5</v>
       </c>
-      <c r="G8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="G12" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="9">
         <v>3.43</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F13" s="9">
         <v>1.5</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G13" s="9">
         <v>8.0</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H13" s="9">
         <v>4.0</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I13" s="9">
         <v>5.0</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J13" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="13">
+      <c r="B14" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="9">
         <v>6.86</v>
       </c>
-      <c r="F10" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="13">
+      <c r="F14" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="9">
         <v>8.0</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H14" s="9">
         <v>4.0</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I14" s="9">
         <v>5.0</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J14" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B15" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="9">
+        <v>6.86</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>7.0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>2.0</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="13">
+      <c r="B16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="9">
         <v>6.86</v>
       </c>
-      <c r="F11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="13">
-        <v>7.0</v>
-      </c>
-      <c r="H11" s="13">
+      <c r="F16" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="9">
+        <v>6.86</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="15">
+        <v>13.0</v>
+      </c>
+      <c r="H18" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="15">
+        <v>8.0</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F20" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G20" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1.2</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F21" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G21" s="9">
+        <v>13.0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="14">
         <v>2.0</v>
       </c>
-      <c r="I11" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="13">
-        <v>6.86</v>
-      </c>
-      <c r="F12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="13">
+      <c r="D22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F22" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G22" s="9">
         <v>13.0</v>
       </c>
-      <c r="H12" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="13">
+      <c r="H22" s="9">
+        <v>6.0</v>
+      </c>
+      <c r="I22" s="9">
         <v>8.0</v>
       </c>
-      <c r="J12" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="13">
-        <v>6.86</v>
-      </c>
-      <c r="F13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="J22" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="14">
+        <v>2.0</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F23" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G23" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>4.0</v>
+      </c>
+      <c r="I23" s="9">
+        <v>8.0</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="9">
+        <v>2.0</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="F24" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="G24" s="16">
+        <v>8.0</v>
+      </c>
+      <c r="H24" s="16">
+        <v>4.0</v>
+      </c>
+      <c r="I24" s="16">
+        <v>8.0</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="15">
+        <v>2.0</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3.43</v>
+      </c>
+      <c r="F25" s="18">
+        <v>3.43</v>
+      </c>
+      <c r="G25" s="17">
         <v>13.0</v>
       </c>
-      <c r="H13" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H25" s="17">
+        <v>6.0</v>
+      </c>
+      <c r="I25" s="17">
         <v>8.0</v>
       </c>
-      <c r="J13" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="15">
-        <v>13.0</v>
-      </c>
-      <c r="H14" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I14" s="15">
-        <v>8.0</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="13">
-        <v>3.2</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>13.0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="13">
+      <c r="J25" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="18">
         <v>3.43</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F26" s="18">
         <v>3.43</v>
       </c>
-      <c r="G16" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="I16" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="13">
+      <c r="G26" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="18">
         <v>3.43</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F27" s="18">
         <v>3.43</v>
       </c>
-      <c r="G17" s="13">
-        <v>13.0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>6.0</v>
-      </c>
-      <c r="I17" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="F18" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="G18" s="13">
-        <v>13.0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>6.0</v>
-      </c>
-      <c r="I18" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="14">
-        <v>2.0</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="F19" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="G19" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="H19" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="I19" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="F20" s="13">
-        <v>3.43</v>
-      </c>
-      <c r="G20" s="16">
-        <v>8.0</v>
-      </c>
-      <c r="H20" s="16">
-        <v>4.0</v>
-      </c>
-      <c r="I20" s="16">
-        <v>8.0</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="15">
-        <v>2.0</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="18">
-        <v>3.43</v>
-      </c>
-      <c r="F21" s="18">
-        <v>3.43</v>
-      </c>
-      <c r="G21" s="17">
-        <v>13.0</v>
-      </c>
-      <c r="H21" s="17">
-        <v>6.0</v>
-      </c>
-      <c r="I21" s="17">
-        <v>8.0</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="18">
-        <v>3.43</v>
-      </c>
-      <c r="F22" s="18">
-        <v>3.43</v>
-      </c>
-      <c r="G22" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="17" t="s">
+      <c r="G27" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="17">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="17" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="15">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="18">
-        <v>3.43</v>
-      </c>
-      <c r="F23" s="18">
-        <v>3.43</v>
-      </c>
-      <c r="G23" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/flume_tank_2026/data/flume_tank_data_2026.xlsx
+++ b/analysis/flume_tank_2026/data/flume_tank_data_2026.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="All" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="rig" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="All" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="rig" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -335,7 +335,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -357,6 +357,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -452,6 +455,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2005,7 +2012,7 @@
         <v>337.7</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="5">
+      <c r="J16" s="8">
         <v>95.7</v>
       </c>
       <c r="K16" s="5">
@@ -2024,7 +2031,7 @@
       <c r="O16" s="5">
         <v>22.8</v>
       </c>
-      <c r="P16" s="5">
+      <c r="P16" s="8">
         <v>21.0</v>
       </c>
       <c r="Q16" s="6">
@@ -2341,8 +2348,8 @@
         <v>333.9</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="5">
-        <v>224.0</v>
+      <c r="J20" s="8">
+        <v>117.2</v>
       </c>
       <c r="K20" s="5">
         <v>4.0</v>
@@ -2388,11 +2395,11 @@
       <c r="X20" s="5">
         <v>4.5</v>
       </c>
-      <c r="Y20" s="5">
-        <v>12.7</v>
-      </c>
-      <c r="Z20" s="5">
-        <v>353.0</v>
+      <c r="Y20" s="8">
+        <v>89.5</v>
+      </c>
+      <c r="Z20" s="8">
+        <v>50.3</v>
       </c>
       <c r="AA20" s="7">
         <v>39.9</v>
@@ -2427,8 +2434,8 @@
         <v>333.9</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="5">
-        <v>224.0</v>
+      <c r="J21" s="8">
+        <v>115.5</v>
       </c>
       <c r="K21" s="5">
         <v>4.0</v>
@@ -2474,11 +2481,11 @@
       <c r="X21" s="5">
         <v>5.8</v>
       </c>
-      <c r="Y21" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="Z21" s="5">
-        <v>305.5</v>
+      <c r="Y21" s="8">
+        <v>77.2</v>
+      </c>
+      <c r="Z21" s="8">
+        <v>75.4</v>
       </c>
       <c r="AA21" s="7">
         <v>39.2</v>
@@ -2513,8 +2520,8 @@
         <v>333.9</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="5">
-        <v>224.0</v>
+      <c r="J22" s="8">
+        <v>115.4</v>
       </c>
       <c r="K22" s="5">
         <v>4.0</v>
@@ -2560,11 +2567,11 @@
       <c r="X22" s="5">
         <v>7.3</v>
       </c>
-      <c r="Y22" s="5">
-        <v>27.6</v>
-      </c>
-      <c r="Z22" s="5">
-        <v>265.2</v>
+      <c r="Y22" s="8">
+        <v>66.2</v>
+      </c>
+      <c r="Z22" s="8">
+        <v>110.5</v>
       </c>
       <c r="AA22" s="7">
         <v>39.1</v>
@@ -2599,8 +2606,8 @@
         <v>333.9</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="5">
-        <v>224.0</v>
+      <c r="J23" s="8">
+        <v>105.8</v>
       </c>
       <c r="K23" s="5">
         <v>6.0</v>
@@ -2646,11 +2653,11 @@
       <c r="X23" s="5">
         <v>3.0</v>
       </c>
-      <c r="Y23" s="5">
-        <v>9.1</v>
-      </c>
-      <c r="Z23" s="5">
-        <v>332.3</v>
+      <c r="Y23" s="8">
+        <v>110.2</v>
+      </c>
+      <c r="Z23" s="8">
+        <v>27.5</v>
       </c>
       <c r="AA23" s="7">
         <v>33.2</v>
@@ -2685,8 +2692,8 @@
         <v>333.9</v>
       </c>
       <c r="I24" s="6"/>
-      <c r="J24" s="5">
-        <v>224.0</v>
+      <c r="J24" s="8">
+        <v>104.1</v>
       </c>
       <c r="K24" s="5">
         <v>6.0</v>
@@ -2732,11 +2739,11 @@
       <c r="X24" s="5">
         <v>4.2</v>
       </c>
-      <c r="Y24" s="5">
-        <v>14.5</v>
-      </c>
-      <c r="Z24" s="5">
-        <v>293.0</v>
+      <c r="Y24" s="8">
+        <v>94.5</v>
+      </c>
+      <c r="Z24" s="8">
+        <v>44.8</v>
       </c>
       <c r="AA24" s="7">
         <v>32.5</v>
@@ -2769,8 +2776,8 @@
         <v>333.9</v>
       </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="5">
-        <v>224.0</v>
+      <c r="J25" s="8">
+        <v>105.7</v>
       </c>
       <c r="K25" s="5">
         <v>6.0</v>
@@ -2778,7 +2785,7 @@
       <c r="L25" s="4">
         <v>3.0</v>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="9">
         <v>17.5</v>
       </c>
       <c r="N25" s="6">
@@ -2816,11 +2823,11 @@
       <c r="X25" s="5">
         <v>5.5</v>
       </c>
-      <c r="Y25" s="5">
-        <v>21.3</v>
-      </c>
-      <c r="Z25" s="5">
-        <v>260.0</v>
+      <c r="Y25" s="8">
+        <v>81.0</v>
+      </c>
+      <c r="Z25" s="8">
+        <v>68.4</v>
       </c>
       <c r="AA25" s="7">
         <v>33.1</v>
@@ -2853,8 +2860,8 @@
         <v>333.9</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="5">
-        <v>224.0</v>
+      <c r="J26" s="8">
+        <v>105.7</v>
       </c>
       <c r="K26" s="5">
         <v>6.0</v>
@@ -2900,11 +2907,11 @@
       <c r="X26" s="5">
         <v>7.0</v>
       </c>
-      <c r="Y26" s="5">
-        <v>30.2</v>
-      </c>
-      <c r="Z26" s="5">
-        <v>231.1</v>
+      <c r="Y26" s="8">
+        <v>70.8</v>
+      </c>
+      <c r="Z26" s="8">
+        <v>98.6</v>
       </c>
       <c r="AA26" s="7">
         <v>33.1</v>
@@ -2937,8 +2944,8 @@
         <v>333.9</v>
       </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="5">
-        <v>224.0</v>
+      <c r="J27" s="8">
+        <v>104.8</v>
       </c>
       <c r="K27" s="5">
         <v>6.0</v>
@@ -2984,11 +2991,11 @@
       <c r="X27" s="5">
         <v>8.4</v>
       </c>
-      <c r="Y27" s="5">
-        <v>40.7</v>
-      </c>
-      <c r="Z27" s="5">
-        <v>207.6</v>
+      <c r="Y27" s="8">
+        <v>61.1</v>
+      </c>
+      <c r="Z27" s="8">
+        <v>138.4</v>
       </c>
       <c r="AA27" s="7">
         <v>32.7</v>
@@ -3021,8 +3028,8 @@
         <v>333.9</v>
       </c>
       <c r="I28" s="6"/>
-      <c r="J28" s="5">
-        <v>224.0</v>
+      <c r="J28" s="8">
+        <v>98.4</v>
       </c>
       <c r="K28" s="5">
         <v>12.0</v>
@@ -3068,11 +3075,11 @@
       <c r="X28" s="5">
         <v>2.9</v>
       </c>
-      <c r="Y28" s="5">
-        <v>14.6</v>
-      </c>
-      <c r="Z28" s="5">
-        <v>200.9</v>
+      <c r="Y28" s="8">
+        <v>115.0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>25.5</v>
       </c>
       <c r="AA28" s="7">
         <v>26.4</v>
@@ -3107,8 +3114,8 @@
         <v>333.9</v>
       </c>
       <c r="I29" s="6"/>
-      <c r="J29" s="5">
-        <v>224.0</v>
+      <c r="J29" s="8">
+        <v>96.6</v>
       </c>
       <c r="K29" s="5">
         <v>12.0</v>
@@ -3154,11 +3161,11 @@
       <c r="X29" s="5">
         <v>4.1</v>
       </c>
-      <c r="Y29" s="5">
-        <v>22.2</v>
-      </c>
-      <c r="Z29" s="5">
-        <v>186.0</v>
+      <c r="Y29" s="8">
+        <v>100.6</v>
+      </c>
+      <c r="Z29" s="8">
+        <v>41.0</v>
       </c>
       <c r="AA29" s="7">
         <v>25.8</v>
@@ -3191,8 +3198,8 @@
         <v>333.9</v>
       </c>
       <c r="I30" s="6"/>
-      <c r="J30" s="5">
-        <v>224.0</v>
+      <c r="J30" s="8">
+        <v>96.6</v>
       </c>
       <c r="K30" s="5">
         <v>12.0</v>
@@ -3237,11 +3244,11 @@
       <c r="X30" s="5">
         <v>5.4</v>
       </c>
-      <c r="Y30" s="5">
-        <v>31.2</v>
-      </c>
-      <c r="Z30" s="5">
-        <v>172.6</v>
+      <c r="Y30" s="8">
+        <v>88.5</v>
+      </c>
+      <c r="Z30" s="8">
+        <v>60.8</v>
       </c>
       <c r="AA30" s="7">
         <v>25.8</v>
@@ -3274,8 +3281,8 @@
         <v>333.9</v>
       </c>
       <c r="I31" s="6"/>
-      <c r="J31" s="5">
-        <v>224.0</v>
+      <c r="J31" s="8">
+        <v>95.2</v>
       </c>
       <c r="K31" s="5">
         <v>12.0</v>
@@ -3321,11 +3328,11 @@
       <c r="X31" s="5">
         <v>6.8</v>
       </c>
-      <c r="Y31" s="5">
-        <v>42.8</v>
-      </c>
-      <c r="Z31" s="5">
-        <v>159.4</v>
+      <c r="Y31" s="8">
+        <v>75.6</v>
+      </c>
+      <c r="Z31" s="8">
+        <v>90.3</v>
       </c>
       <c r="AA31" s="7">
         <v>25.4</v>
@@ -3358,8 +3365,8 @@
         <v>333.9</v>
       </c>
       <c r="I32" s="6"/>
-      <c r="J32" s="5">
-        <v>224.0</v>
+      <c r="J32" s="8">
+        <v>93.6</v>
       </c>
       <c r="K32" s="5">
         <v>12.0</v>
@@ -3405,11 +3412,11 @@
       <c r="X32" s="5">
         <v>8.3</v>
       </c>
-      <c r="Y32" s="5">
-        <v>56.1</v>
-      </c>
-      <c r="Z32" s="5">
-        <v>147.9</v>
+      <c r="Y32" s="8">
+        <v>67.1</v>
+      </c>
+      <c r="Z32" s="8">
+        <v>123.6</v>
       </c>
       <c r="AA32" s="7">
         <v>24.9</v>
@@ -3442,8 +3449,8 @@
         <v>333.9</v>
       </c>
       <c r="I33" s="6"/>
-      <c r="J33" s="5">
-        <v>224.0</v>
+      <c r="J33" s="8">
+        <v>80.5</v>
       </c>
       <c r="K33" s="5">
         <v>12.0</v>
@@ -3489,11 +3496,11 @@
       <c r="X33" s="5">
         <v>4.1</v>
       </c>
-      <c r="Y33" s="5">
-        <v>21.9</v>
-      </c>
-      <c r="Z33" s="5">
-        <v>186.5</v>
+      <c r="Y33" s="8">
+        <v>103.2</v>
+      </c>
+      <c r="Z33" s="8">
+        <v>39.6</v>
       </c>
       <c r="AA33" s="7">
         <v>20.9</v>
@@ -3526,8 +3533,8 @@
         <v>333.9</v>
       </c>
       <c r="I34" s="6"/>
-      <c r="J34" s="5">
-        <v>224.0</v>
+      <c r="J34" s="8">
+        <v>78.6</v>
       </c>
       <c r="K34" s="5">
         <v>12.0</v>
@@ -3573,11 +3580,11 @@
       <c r="X34" s="5">
         <v>5.4</v>
       </c>
-      <c r="Y34" s="5">
-        <v>31.7</v>
-      </c>
-      <c r="Z34" s="5">
-        <v>171.9</v>
+      <c r="Y34" s="8">
+        <v>93.3</v>
+      </c>
+      <c r="Z34" s="8">
+        <v>58.4</v>
       </c>
       <c r="AA34" s="7">
         <v>20.3</v>
@@ -3610,8 +3617,8 @@
         <v>333.9</v>
       </c>
       <c r="I35" s="6"/>
-      <c r="J35" s="5">
-        <v>224.0</v>
+      <c r="J35" s="8">
+        <v>76.9</v>
       </c>
       <c r="K35" s="5">
         <v>12.0</v>
@@ -3657,11 +3664,11 @@
       <c r="X35" s="5">
         <v>6.9</v>
       </c>
-      <c r="Y35" s="5">
-        <v>43.5</v>
-      </c>
-      <c r="Z35" s="5">
-        <v>158.7</v>
+      <c r="Y35" s="8">
+        <v>83.9</v>
+      </c>
+      <c r="Z35" s="8">
+        <v>82.2</v>
       </c>
       <c r="AA35" s="7">
         <v>19.8</v>
@@ -3694,8 +3701,8 @@
         <v>333.9</v>
       </c>
       <c r="I36" s="6"/>
-      <c r="J36" s="5">
-        <v>224.0</v>
+      <c r="J36" s="8">
+        <v>117.0</v>
       </c>
       <c r="K36" s="5">
         <v>27.4</v>
@@ -3741,11 +3748,11 @@
       <c r="X36" s="5">
         <v>5.4</v>
       </c>
-      <c r="Y36" s="5">
-        <v>59.0</v>
-      </c>
-      <c r="Z36" s="5">
-        <v>91.4</v>
+      <c r="Y36" s="8">
+        <v>85.2</v>
+      </c>
+      <c r="Z36" s="8">
+        <v>63.3</v>
       </c>
       <c r="AA36" s="7">
         <v>24.2</v>
@@ -3950,8 +3957,8 @@
         <v>333.9</v>
       </c>
       <c r="I39" s="6"/>
-      <c r="J39" s="5">
-        <v>92.8</v>
+      <c r="J39" s="8">
+        <v>92.9</v>
       </c>
       <c r="K39" s="5">
         <v>27.4</v>
@@ -6814,7 +6821,7 @@
       <c r="C73" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D73" s="9" t="s">
+      <c r="D73" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E73" s="5">
@@ -6900,7 +6907,7 @@
       <c r="C74" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D74" s="9" t="s">
+      <c r="D74" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E74" s="5">
@@ -6986,7 +6993,7 @@
       <c r="C75" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D75" s="9" t="s">
+      <c r="D75" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E75" s="5">
@@ -7070,7 +7077,7 @@
       <c r="C76" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D76" s="9" t="s">
+      <c r="D76" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E76" s="5">
@@ -7154,7 +7161,7 @@
       <c r="C77" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="9" t="s">
+      <c r="D77" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E77" s="5">
@@ -7240,7 +7247,7 @@
       <c r="C78" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D78" s="9" t="s">
+      <c r="D78" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E78" s="5">
@@ -7324,7 +7331,7 @@
       <c r="C79" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="9" t="s">
+      <c r="D79" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E79" s="5">
@@ -7410,7 +7417,7 @@
       <c r="C80" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D80" s="9" t="s">
+      <c r="D80" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E80" s="5">
@@ -7429,8 +7436,8 @@
       <c r="J80" s="5">
         <v>71.4</v>
       </c>
-      <c r="K80" s="5">
-        <v>0.0</v>
+      <c r="K80" s="8">
+        <v>29.3</v>
       </c>
       <c r="L80" s="4">
         <v>2.0</v>
@@ -7471,8 +7478,8 @@
         <v>125.3</v>
       </c>
       <c r="Z80" s="5"/>
-      <c r="AA80" s="7">
-        <v>23.5</v>
+      <c r="AA80" s="8">
+        <v>25.3</v>
       </c>
       <c r="AB80" s="4" t="s">
         <v>62</v>
@@ -7488,7 +7495,7 @@
       <c r="C81" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E81" s="5">
@@ -7507,8 +7514,8 @@
       <c r="J81" s="5">
         <v>73.0</v>
       </c>
-      <c r="K81" s="5">
-        <v>0.0</v>
+      <c r="K81" s="8">
+        <v>29.3</v>
       </c>
       <c r="L81" s="4">
         <v>3.0</v>
@@ -7564,11 +7571,11 @@
       <c r="C82" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D82" s="9" t="s">
+      <c r="D82" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E82" s="5">
-        <v>28.0</v>
+      <c r="E82" s="8">
+        <v>26.1</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>30</v>
@@ -7583,8 +7590,8 @@
       <c r="J82" s="5">
         <v>71.3</v>
       </c>
-      <c r="K82" s="5">
-        <v>0.0</v>
+      <c r="K82" s="8">
+        <v>29.3</v>
       </c>
       <c r="L82" s="4">
         <v>4.0</v>
@@ -7625,8 +7632,8 @@
         <v>86.5</v>
       </c>
       <c r="Z82" s="5"/>
-      <c r="AA82" s="7">
-        <v>23.5</v>
+      <c r="AA82" s="8">
+        <v>25.3</v>
       </c>
       <c r="AB82" s="6"/>
     </row>
@@ -7640,11 +7647,11 @@
       <c r="C83" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D83" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E83" s="5">
-        <v>28.0</v>
+      <c r="E83" s="8">
+        <v>26.1</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>30</v>
@@ -7659,8 +7666,8 @@
       <c r="J83" s="5">
         <v>83.5</v>
       </c>
-      <c r="K83" s="5">
-        <v>0.0</v>
+      <c r="K83" s="8">
+        <v>29.3</v>
       </c>
       <c r="L83" s="4">
         <v>2.0</v>
@@ -7701,8 +7708,8 @@
         <v>122.9</v>
       </c>
       <c r="Z83" s="5"/>
-      <c r="AA83" s="7">
-        <v>28.3</v>
+      <c r="AA83" s="8">
+        <v>30.5</v>
       </c>
       <c r="AB83" s="6"/>
     </row>
@@ -7716,11 +7723,11 @@
       <c r="C84" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D84" s="9" t="s">
+      <c r="D84" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E84" s="5">
-        <v>28.0</v>
+      <c r="E84" s="8">
+        <v>26.1</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>30</v>
@@ -7735,8 +7742,8 @@
       <c r="J84" s="5">
         <v>82.9</v>
       </c>
-      <c r="K84" s="5">
-        <v>0.0</v>
+      <c r="K84" s="8">
+        <v>29.3</v>
       </c>
       <c r="L84" s="4">
         <v>3.0</v>
@@ -7777,8 +7784,8 @@
         <v>98.9</v>
       </c>
       <c r="Z84" s="5"/>
-      <c r="AA84" s="7">
-        <v>28.2</v>
+      <c r="AA84" s="8">
+        <v>30.3</v>
       </c>
       <c r="AB84" s="6"/>
     </row>
@@ -7792,11 +7799,11 @@
       <c r="C85" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D85" s="9" t="s">
+      <c r="D85" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E85" s="5">
-        <v>28.0</v>
+      <c r="E85" s="8">
+        <v>26.1</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>30</v>
@@ -7811,8 +7818,8 @@
       <c r="J85" s="5">
         <v>83.8</v>
       </c>
-      <c r="K85" s="5">
-        <v>0.0</v>
+      <c r="K85" s="8">
+        <v>29.3</v>
       </c>
       <c r="L85" s="4">
         <v>4.0</v>
@@ -7853,8 +7860,8 @@
         <v>83.5</v>
       </c>
       <c r="Z85" s="5"/>
-      <c r="AA85" s="5">
-        <v>28.6</v>
+      <c r="AA85" s="8">
+        <v>30.8</v>
       </c>
       <c r="AB85" s="6"/>
     </row>
@@ -7868,7 +7875,7 @@
       <c r="C86" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D86" s="9" t="s">
+      <c r="D86" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E86" s="5">
@@ -7887,8 +7894,8 @@
       <c r="J86" s="5">
         <v>69.6</v>
       </c>
-      <c r="K86" s="5">
-        <v>0.0</v>
+      <c r="K86" s="8">
+        <v>29.3</v>
       </c>
       <c r="L86" s="4">
         <v>2.0</v>
@@ -7896,7 +7903,7 @@
       <c r="M86" s="4">
         <v>16.0</v>
       </c>
-      <c r="N86" s="10">
+      <c r="N86" s="11">
         <f t="shared" ref="N86:N87" si="19">2.01*8</f>
         <v>16.08</v>
       </c>
@@ -7909,7 +7916,7 @@
       <c r="Q86" s="6">
         <v>17.9</v>
       </c>
-      <c r="R86" s="10">
+      <c r="R86" s="11">
         <f>0.884*8</f>
         <v>7.072</v>
       </c>
@@ -7944,7 +7951,7 @@
       <c r="C87" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D87" s="9" t="s">
+      <c r="D87" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E87" s="5">
@@ -7963,8 +7970,8 @@
       <c r="J87" s="5">
         <v>69.6</v>
       </c>
-      <c r="K87" s="5">
-        <v>0.0</v>
+      <c r="K87" s="8">
+        <v>29.3</v>
       </c>
       <c r="L87" s="4">
         <v>3.0</v>
@@ -8020,7 +8027,7 @@
       <c r="C88" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D88" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E88" s="5">
@@ -8039,8 +8046,8 @@
       <c r="J88" s="5">
         <v>69.7</v>
       </c>
-      <c r="K88" s="5">
-        <v>0.0</v>
+      <c r="K88" s="8">
+        <v>29.3</v>
       </c>
       <c r="L88" s="4">
         <v>4.0</v>
@@ -8096,7 +8103,7 @@
       <c r="C89" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="D89" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E89" s="5">
@@ -8115,8 +8122,8 @@
       <c r="J89" s="5">
         <v>80.7</v>
       </c>
-      <c r="K89" s="5">
-        <v>0.0</v>
+      <c r="K89" s="8">
+        <v>29.3</v>
       </c>
       <c r="L89" s="4">
         <v>2.0</v>
@@ -8172,7 +8179,7 @@
       <c r="C90" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D90" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E90" s="5">
@@ -8191,8 +8198,8 @@
       <c r="J90" s="5">
         <v>80.6</v>
       </c>
-      <c r="K90" s="5">
-        <v>0.0</v>
+      <c r="K90" s="8">
+        <v>29.3</v>
       </c>
       <c r="L90" s="4">
         <v>3.0</v>
@@ -8248,7 +8255,7 @@
       <c r="C91" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D91" s="9" t="s">
+      <c r="D91" s="10" t="s">
         <v>55</v>
       </c>
       <c r="E91" s="5">
@@ -8267,8 +8274,8 @@
       <c r="J91" s="5">
         <v>80.8</v>
       </c>
-      <c r="K91" s="5">
-        <v>0.0</v>
+      <c r="K91" s="8">
+        <v>27.4</v>
       </c>
       <c r="L91" s="4">
         <v>4.0</v>
@@ -8585,17 +8592,17 @@
       <c r="D95" s="4">
         <v>2.0</v>
       </c>
-      <c r="E95" s="11">
+      <c r="E95" s="12">
         <v>27.9</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
       <c r="I95" s="6"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
+      <c r="J95" s="13"/>
+      <c r="K95" s="13"/>
       <c r="L95" s="4">
         <v>3.0</v>
       </c>
@@ -8606,22 +8613,22 @@
         <f>1.99*8</f>
         <v>15.92</v>
       </c>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
+      <c r="O95" s="13"/>
+      <c r="P95" s="13"/>
       <c r="Q95" s="6"/>
       <c r="R95" s="6">
         <f>0.593*8</f>
         <v>4.744</v>
       </c>
-      <c r="S95" s="12"/>
-      <c r="T95" s="12"/>
-      <c r="U95" s="12"/>
-      <c r="V95" s="12"/>
-      <c r="W95" s="12"/>
-      <c r="X95" s="12"/>
-      <c r="Y95" s="12"/>
-      <c r="Z95" s="12"/>
-      <c r="AA95" s="13"/>
+      <c r="S95" s="13"/>
+      <c r="T95" s="13"/>
+      <c r="U95" s="13"/>
+      <c r="V95" s="13"/>
+      <c r="W95" s="13"/>
+      <c r="X95" s="13"/>
+      <c r="Y95" s="13"/>
+      <c r="Z95" s="13"/>
+      <c r="AA95" s="14"/>
       <c r="AB95" s="4" t="s">
         <v>70</v>
       </c>
@@ -8992,866 +8999,866 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <v>1.2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>3.43</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="10">
         <v>3.43</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>8.0</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>1.0</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>8.0</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <v>1.2</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <v>3.43</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="10">
         <v>3.43</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <v>8.0</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <v>4.0</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <v>8.0</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>1.2</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>3.43</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <v>3.43</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <v>8.0</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <v>4.0</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <v>8.0</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>1.2</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>3.43</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>0.75</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>8.0</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>4.0</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>8.0</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="10" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>1.2</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>3.43</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="10">
         <v>0.75</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>8.0</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>4.0</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <v>8.0</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="10" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <v>1.0</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>3.43</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <v>0.5</v>
       </c>
-      <c r="G7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="9" t="s">
+      <c r="G7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <v>1.0</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="10">
         <v>3.43</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="10">
         <v>0.75</v>
       </c>
-      <c r="G8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="9" t="s">
+      <c r="G8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <v>1.0</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <v>3.43</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="10">
         <v>0.75</v>
       </c>
-      <c r="G9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="9" t="s">
+      <c r="G9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J9" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="15">
         <v>1.0</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="10">
         <v>3.43</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="10">
         <v>3.43</v>
       </c>
-      <c r="G10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="9" t="s">
+      <c r="G10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="15">
         <v>1.0</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="10">
         <v>3.43</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="10">
         <v>3.43</v>
       </c>
-      <c r="G11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="9" t="s">
+      <c r="G11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="15">
         <v>1.0</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <v>3.43</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="10">
         <v>1.5</v>
       </c>
-      <c r="G12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="9" t="s">
+      <c r="G12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <v>1.2</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <v>3.43</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="10">
         <v>1.5</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="10">
         <v>8.0</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="10">
         <v>4.0</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <v>5.0</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <v>1.2</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="10">
         <v>6.86</v>
       </c>
-      <c r="F14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="9">
+      <c r="F14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="10">
         <v>8.0</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="10">
         <v>4.0</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <v>5.0</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <v>6.86</v>
       </c>
-      <c r="F15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="9">
+      <c r="F15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="10">
         <v>7.0</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="10">
         <v>2.0</v>
       </c>
-      <c r="I15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="9" t="s">
+      <c r="I15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <v>6.86</v>
       </c>
-      <c r="F16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="9">
+      <c r="F16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="10">
         <v>13.0</v>
       </c>
-      <c r="H16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="9">
+      <c r="H16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="10">
         <v>8.0</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>6.86</v>
       </c>
-      <c r="F17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="9">
+      <c r="F17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="10">
         <v>13.0</v>
       </c>
-      <c r="H17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="9">
+      <c r="H17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="10">
         <v>8.0</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="10" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="10">
         <v>3.2</v>
       </c>
-      <c r="F18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="F18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="16">
         <v>13.0</v>
       </c>
-      <c r="H18" s="15">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="H18" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="16">
         <v>8.0</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <v>3.2</v>
       </c>
-      <c r="F19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="9">
+      <c r="F19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="10">
         <v>13.0</v>
       </c>
-      <c r="H19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="9">
+      <c r="H19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="10">
         <v>8.0</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="10">
         <v>1.2</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="10">
         <v>3.43</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="10">
         <v>3.43</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="10">
         <v>8.0</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="10">
         <v>4.0</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="10">
         <v>8.0</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="10">
         <v>1.2</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <v>3.43</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="10">
         <v>3.43</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="10">
         <v>13.0</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="10">
         <v>6.0</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="10">
         <v>8.0</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="10" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="15">
         <v>2.0</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="10">
         <v>3.43</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="10">
         <v>3.43</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="10">
         <v>13.0</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="10">
         <v>6.0</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <v>8.0</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="10" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="15">
         <v>2.0</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>3.43</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>3.43</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="10">
         <v>8.0</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <v>4.0</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <v>8.0</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="10" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="10">
         <v>2.0</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="10">
         <v>3.43</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="10">
         <v>3.43</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="17">
         <v>8.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>4.0</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>8.0</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J24" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="s">
+      <c r="A25" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="16">
         <v>2.0</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="19">
         <v>3.43</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="19">
         <v>3.43</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="18">
         <v>13.0</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="18">
         <v>6.0</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="18">
         <v>8.0</v>
       </c>
-      <c r="J25" s="17" t="s">
+      <c r="J25" s="18" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="16">
         <v>1.0</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="19">
         <v>3.43</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="19">
         <v>3.43</v>
       </c>
-      <c r="G26" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="I26" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="J26" s="17" t="s">
+      <c r="G26" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="J26" s="18" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="s">
+      <c r="A27" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="16">
         <v>1.0</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="19">
         <v>3.43</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="19">
         <v>3.43</v>
       </c>
-      <c r="G27" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="17">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="17" t="s">
+      <c r="G27" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="18" t="s">
         <v>78</v>
       </c>
     </row>

--- a/analysis/flume_tank_2026/data/flume_tank_data_2026.xlsx
+++ b/analysis/flume_tank_2026/data/flume_tank_data_2026.xlsx
@@ -356,10 +356,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -831,8 +831,8 @@
         <v>337.7</v>
       </c>
       <c r="I2" s="6"/>
-      <c r="J2" s="5">
-        <v>111.6</v>
+      <c r="J2" s="7">
+        <v>69.0</v>
       </c>
       <c r="K2" s="4">
         <v>27.4</v>
@@ -917,8 +917,8 @@
         <v>337.7</v>
       </c>
       <c r="I3" s="6"/>
-      <c r="J3" s="5">
-        <v>111.9</v>
+      <c r="J3" s="7">
+        <v>69.1</v>
       </c>
       <c r="K3" s="4">
         <v>27.4</v>
@@ -970,7 +970,7 @@
       <c r="Z3" s="5">
         <v>61.5</v>
       </c>
-      <c r="AA3" s="7">
+      <c r="AA3" s="8">
         <v>22.8</v>
       </c>
       <c r="AB3" s="4" t="s">
@@ -990,7 +990,7 @@
       <c r="D4" s="4">
         <v>1.2</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <v>27.9</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -1003,8 +1003,8 @@
         <v>337.7</v>
       </c>
       <c r="I4" s="6"/>
-      <c r="J4" s="5">
-        <v>93.8</v>
+      <c r="J4" s="7">
+        <v>58.6</v>
       </c>
       <c r="K4" s="5">
         <v>27.4</v>
@@ -1056,7 +1056,7 @@
       <c r="Z4" s="5">
         <v>40.7</v>
       </c>
-      <c r="AA4" s="7">
+      <c r="AA4" s="8">
         <v>18.6</v>
       </c>
     </row>
@@ -1086,8 +1086,8 @@
         <v>337.7</v>
       </c>
       <c r="I5" s="6"/>
-      <c r="J5" s="5">
-        <v>93.2</v>
+      <c r="J5" s="7">
+        <v>58.1</v>
       </c>
       <c r="K5" s="5">
         <v>27.4</v>
@@ -1139,7 +1139,7 @@
       <c r="Z5" s="5">
         <v>60.9</v>
       </c>
-      <c r="AA5" s="7">
+      <c r="AA5" s="8">
         <v>18.5</v>
       </c>
       <c r="AB5" s="6"/>
@@ -1170,8 +1170,8 @@
         <v>337.7</v>
       </c>
       <c r="I6" s="6"/>
-      <c r="J6" s="5">
-        <v>92.2</v>
+      <c r="J6" s="7">
+        <v>57.6</v>
       </c>
       <c r="K6" s="5">
         <v>27.4</v>
@@ -1223,7 +1223,7 @@
       <c r="Z6" s="5">
         <v>84.8</v>
       </c>
-      <c r="AA6" s="7">
+      <c r="AA6" s="8">
         <v>18.2</v>
       </c>
       <c r="AB6" s="6"/>
@@ -1254,8 +1254,8 @@
         <v>337.7</v>
       </c>
       <c r="I7" s="6"/>
-      <c r="J7" s="5">
-        <v>114.9</v>
+      <c r="J7" s="7">
+        <v>71.0</v>
       </c>
       <c r="K7" s="5">
         <v>27.4</v>
@@ -1307,7 +1307,7 @@
       <c r="Z7" s="5">
         <v>26.4</v>
       </c>
-      <c r="AA7" s="7">
+      <c r="AA7" s="8">
         <v>23.4</v>
       </c>
       <c r="AB7" s="6"/>
@@ -1338,8 +1338,8 @@
         <v>337.7</v>
       </c>
       <c r="I8" s="6"/>
-      <c r="J8" s="5">
-        <v>114.5</v>
+      <c r="J8" s="7">
+        <v>70.6</v>
       </c>
       <c r="K8" s="5">
         <v>27.4</v>
@@ -1391,7 +1391,7 @@
       <c r="Z8" s="5">
         <v>43.0</v>
       </c>
-      <c r="AA8" s="7">
+      <c r="AA8" s="8">
         <v>23.4</v>
       </c>
       <c r="AB8" s="6"/>
@@ -1422,8 +1422,8 @@
         <v>337.7</v>
       </c>
       <c r="I9" s="6"/>
-      <c r="J9" s="5">
-        <v>113.6</v>
+      <c r="J9" s="7">
+        <v>70.1</v>
       </c>
       <c r="K9" s="5">
         <v>27.4</v>
@@ -1475,7 +1475,7 @@
       <c r="Z9" s="5">
         <v>63.9</v>
       </c>
-      <c r="AA9" s="7">
+      <c r="AA9" s="8">
         <v>23.2</v>
       </c>
       <c r="AB9" s="6"/>
@@ -1506,8 +1506,8 @@
         <v>337.7</v>
       </c>
       <c r="I10" s="6"/>
-      <c r="J10" s="5">
-        <v>115.7</v>
+      <c r="J10" s="7">
+        <v>71.2</v>
       </c>
       <c r="K10" s="5">
         <v>27.4</v>
@@ -1559,7 +1559,7 @@
       <c r="Z10" s="5">
         <v>98.1</v>
       </c>
-      <c r="AA10" s="7">
+      <c r="AA10" s="8">
         <v>23.7</v>
       </c>
       <c r="AB10" s="6"/>
@@ -1590,8 +1590,8 @@
         <v>337.7</v>
       </c>
       <c r="I11" s="6"/>
-      <c r="J11" s="5">
-        <v>117.3</v>
+      <c r="J11" s="7">
+        <v>72.2</v>
       </c>
       <c r="K11" s="5">
         <v>27.4</v>
@@ -1643,7 +1643,7 @@
       <c r="Z11" s="5">
         <v>140.3</v>
       </c>
-      <c r="AA11" s="7">
+      <c r="AA11" s="8">
         <v>24.1</v>
       </c>
       <c r="AB11" s="6"/>
@@ -1674,8 +1674,8 @@
         <v>337.7</v>
       </c>
       <c r="I12" s="6"/>
-      <c r="J12" s="5">
-        <v>100.2</v>
+      <c r="J12" s="7">
+        <v>87.6</v>
       </c>
       <c r="K12" s="5">
         <v>6.0</v>
@@ -1727,7 +1727,7 @@
       <c r="Z12" s="5">
         <v>27.9</v>
       </c>
-      <c r="AA12" s="7">
+      <c r="AA12" s="8">
         <v>30.5</v>
       </c>
       <c r="AB12" s="4" t="s">
@@ -1760,8 +1760,8 @@
         <v>337.7</v>
       </c>
       <c r="I13" s="6"/>
-      <c r="J13" s="5">
-        <v>100.1</v>
+      <c r="J13" s="7">
+        <v>87.4</v>
       </c>
       <c r="K13" s="5">
         <v>6.0</v>
@@ -1813,7 +1813,7 @@
       <c r="Z13" s="5">
         <v>44.3</v>
       </c>
-      <c r="AA13" s="7">
+      <c r="AA13" s="8">
         <v>30.5</v>
       </c>
       <c r="AB13" s="6"/>
@@ -1844,8 +1844,8 @@
         <v>337.7</v>
       </c>
       <c r="I14" s="6"/>
-      <c r="J14" s="5">
-        <v>102.2</v>
+      <c r="J14" s="7">
+        <v>89.2</v>
       </c>
       <c r="K14" s="5">
         <v>6.0</v>
@@ -1897,7 +1897,7 @@
       <c r="Z14" s="5">
         <v>71.1</v>
       </c>
-      <c r="AA14" s="7">
+      <c r="AA14" s="8">
         <v>31.4</v>
       </c>
       <c r="AB14" s="6"/>
@@ -1928,8 +1928,8 @@
         <v>337.7</v>
       </c>
       <c r="I15" s="6"/>
-      <c r="J15" s="5">
-        <v>100.6</v>
+      <c r="J15" s="7">
+        <v>87.8</v>
       </c>
       <c r="K15" s="5">
         <v>6.0</v>
@@ -1981,7 +1981,7 @@
       <c r="Z15" s="5">
         <v>102.7</v>
       </c>
-      <c r="AA15" s="7">
+      <c r="AA15" s="8">
         <v>30.8</v>
       </c>
       <c r="AB15" s="6"/>
@@ -2012,8 +2012,8 @@
         <v>337.7</v>
       </c>
       <c r="I16" s="6"/>
-      <c r="J16" s="8">
-        <v>95.7</v>
+      <c r="J16" s="7">
+        <v>84.1</v>
       </c>
       <c r="K16" s="5">
         <v>6.0</v>
@@ -2031,7 +2031,7 @@
       <c r="O16" s="5">
         <v>22.8</v>
       </c>
-      <c r="P16" s="8">
+      <c r="P16" s="7">
         <v>21.0</v>
       </c>
       <c r="Q16" s="6">
@@ -2065,7 +2065,7 @@
       <c r="Z16" s="5">
         <v>138.0</v>
       </c>
-      <c r="AA16" s="7">
+      <c r="AA16" s="8">
         <v>27.6</v>
       </c>
       <c r="AB16" s="6"/>
@@ -2096,8 +2096,8 @@
         <v>337.7</v>
       </c>
       <c r="I17" s="6"/>
-      <c r="J17" s="5">
-        <v>114.5</v>
+      <c r="J17" s="7">
+        <v>99.9</v>
       </c>
       <c r="K17" s="5">
         <v>6.0</v>
@@ -2149,7 +2149,7 @@
       <c r="Z17" s="5">
         <v>48.1</v>
       </c>
-      <c r="AA17" s="7">
+      <c r="AA17" s="8">
         <v>36.0</v>
       </c>
       <c r="AB17" s="6"/>
@@ -2180,8 +2180,8 @@
         <v>337.7</v>
       </c>
       <c r="I18" s="6"/>
-      <c r="J18" s="5">
-        <v>116.5</v>
+      <c r="J18" s="7">
+        <v>101.6</v>
       </c>
       <c r="K18" s="5">
         <v>6.0</v>
@@ -2233,7 +2233,7 @@
       <c r="Z18" s="5">
         <v>75.0</v>
       </c>
-      <c r="AA18" s="7">
+      <c r="AA18" s="8">
         <v>36.9</v>
       </c>
       <c r="AB18" s="6"/>
@@ -2264,8 +2264,8 @@
         <v>337.7</v>
       </c>
       <c r="I19" s="6"/>
-      <c r="J19" s="5">
-        <v>117.2</v>
+      <c r="J19" s="7">
+        <v>102.2</v>
       </c>
       <c r="K19" s="5">
         <v>6.0</v>
@@ -2317,7 +2317,7 @@
       <c r="Z19" s="5">
         <v>116.3</v>
       </c>
-      <c r="AA19" s="7">
+      <c r="AA19" s="8">
         <v>37.2</v>
       </c>
       <c r="AB19" s="6"/>
@@ -2348,8 +2348,8 @@
         <v>333.9</v>
       </c>
       <c r="I20" s="6"/>
-      <c r="J20" s="8">
-        <v>117.2</v>
+      <c r="J20" s="7">
+        <v>106.9</v>
       </c>
       <c r="K20" s="5">
         <v>4.0</v>
@@ -2395,13 +2395,13 @@
       <c r="X20" s="5">
         <v>4.5</v>
       </c>
-      <c r="Y20" s="8">
+      <c r="Y20" s="7">
         <v>89.5</v>
       </c>
-      <c r="Z20" s="8">
+      <c r="Z20" s="7">
         <v>50.3</v>
       </c>
-      <c r="AA20" s="7">
+      <c r="AA20" s="8">
         <v>39.9</v>
       </c>
       <c r="AB20" s="4" t="s">
@@ -2434,8 +2434,8 @@
         <v>333.9</v>
       </c>
       <c r="I21" s="6"/>
-      <c r="J21" s="8">
-        <v>115.5</v>
+      <c r="J21" s="7">
+        <v>105.4</v>
       </c>
       <c r="K21" s="5">
         <v>4.0</v>
@@ -2481,13 +2481,13 @@
       <c r="X21" s="5">
         <v>5.8</v>
       </c>
-      <c r="Y21" s="8">
+      <c r="Y21" s="7">
         <v>77.2</v>
       </c>
-      <c r="Z21" s="8">
+      <c r="Z21" s="7">
         <v>75.4</v>
       </c>
-      <c r="AA21" s="7">
+      <c r="AA21" s="8">
         <v>39.2</v>
       </c>
       <c r="AB21" s="4" t="s">
@@ -2520,8 +2520,8 @@
         <v>333.9</v>
       </c>
       <c r="I22" s="6"/>
-      <c r="J22" s="8">
-        <v>115.4</v>
+      <c r="J22" s="7">
+        <v>105.3</v>
       </c>
       <c r="K22" s="5">
         <v>4.0</v>
@@ -2567,13 +2567,13 @@
       <c r="X22" s="5">
         <v>7.3</v>
       </c>
-      <c r="Y22" s="8">
+      <c r="Y22" s="7">
         <v>66.2</v>
       </c>
-      <c r="Z22" s="8">
+      <c r="Z22" s="7">
         <v>110.5</v>
       </c>
-      <c r="AA22" s="7">
+      <c r="AA22" s="8">
         <v>39.1</v>
       </c>
       <c r="AB22" s="4" t="s">
@@ -2606,8 +2606,8 @@
         <v>333.9</v>
       </c>
       <c r="I23" s="6"/>
-      <c r="J23" s="8">
-        <v>105.8</v>
+      <c r="J23" s="7">
+        <v>92.7</v>
       </c>
       <c r="K23" s="5">
         <v>6.0</v>
@@ -2653,13 +2653,13 @@
       <c r="X23" s="5">
         <v>3.0</v>
       </c>
-      <c r="Y23" s="8">
+      <c r="Y23" s="7">
         <v>110.2</v>
       </c>
-      <c r="Z23" s="8">
+      <c r="Z23" s="7">
         <v>27.5</v>
       </c>
-      <c r="AA23" s="7">
+      <c r="AA23" s="8">
         <v>33.2</v>
       </c>
       <c r="AB23" s="4" t="s">
@@ -2692,8 +2692,8 @@
         <v>333.9</v>
       </c>
       <c r="I24" s="6"/>
-      <c r="J24" s="8">
-        <v>104.1</v>
+      <c r="J24" s="7">
+        <v>91.2</v>
       </c>
       <c r="K24" s="5">
         <v>6.0</v>
@@ -2739,13 +2739,13 @@
       <c r="X24" s="5">
         <v>4.2</v>
       </c>
-      <c r="Y24" s="8">
+      <c r="Y24" s="7">
         <v>94.5</v>
       </c>
-      <c r="Z24" s="8">
+      <c r="Z24" s="7">
         <v>44.8</v>
       </c>
-      <c r="AA24" s="7">
+      <c r="AA24" s="8">
         <v>32.5</v>
       </c>
       <c r="AB24" s="4"/>
@@ -2776,8 +2776,8 @@
         <v>333.9</v>
       </c>
       <c r="I25" s="6"/>
-      <c r="J25" s="8">
-        <v>105.7</v>
+      <c r="J25" s="7">
+        <v>92.6</v>
       </c>
       <c r="K25" s="5">
         <v>6.0</v>
@@ -2823,13 +2823,13 @@
       <c r="X25" s="5">
         <v>5.5</v>
       </c>
-      <c r="Y25" s="8">
+      <c r="Y25" s="7">
         <v>81.0</v>
       </c>
-      <c r="Z25" s="8">
+      <c r="Z25" s="7">
         <v>68.4</v>
       </c>
-      <c r="AA25" s="7">
+      <c r="AA25" s="8">
         <v>33.1</v>
       </c>
       <c r="AB25" s="6"/>
@@ -2860,8 +2860,8 @@
         <v>333.9</v>
       </c>
       <c r="I26" s="6"/>
-      <c r="J26" s="8">
-        <v>105.7</v>
+      <c r="J26" s="7">
+        <v>92.6</v>
       </c>
       <c r="K26" s="5">
         <v>6.0</v>
@@ -2907,13 +2907,13 @@
       <c r="X26" s="5">
         <v>7.0</v>
       </c>
-      <c r="Y26" s="8">
+      <c r="Y26" s="7">
         <v>70.8</v>
       </c>
-      <c r="Z26" s="8">
+      <c r="Z26" s="7">
         <v>98.6</v>
       </c>
-      <c r="AA26" s="7">
+      <c r="AA26" s="8">
         <v>33.1</v>
       </c>
       <c r="AB26" s="6"/>
@@ -2944,8 +2944,8 @@
         <v>333.9</v>
       </c>
       <c r="I27" s="6"/>
-      <c r="J27" s="8">
-        <v>104.8</v>
+      <c r="J27" s="7">
+        <v>91.8</v>
       </c>
       <c r="K27" s="5">
         <v>6.0</v>
@@ -2991,13 +2991,13 @@
       <c r="X27" s="5">
         <v>8.4</v>
       </c>
-      <c r="Y27" s="8">
+      <c r="Y27" s="7">
         <v>61.1</v>
       </c>
-      <c r="Z27" s="8">
+      <c r="Z27" s="7">
         <v>138.4</v>
       </c>
-      <c r="AA27" s="7">
+      <c r="AA27" s="8">
         <v>32.7</v>
       </c>
       <c r="AB27" s="6"/>
@@ -3028,8 +3028,8 @@
         <v>333.9</v>
       </c>
       <c r="I28" s="6"/>
-      <c r="J28" s="8">
-        <v>98.4</v>
+      <c r="J28" s="7">
+        <v>77.1</v>
       </c>
       <c r="K28" s="5">
         <v>12.0</v>
@@ -3075,13 +3075,13 @@
       <c r="X28" s="5">
         <v>2.9</v>
       </c>
-      <c r="Y28" s="8">
+      <c r="Y28" s="7">
         <v>115.0</v>
       </c>
       <c r="Z28" s="3">
         <v>25.5</v>
       </c>
-      <c r="AA28" s="7">
+      <c r="AA28" s="8">
         <v>26.4</v>
       </c>
       <c r="AB28" s="4" t="s">
@@ -3114,8 +3114,8 @@
         <v>333.9</v>
       </c>
       <c r="I29" s="6"/>
-      <c r="J29" s="8">
-        <v>96.6</v>
+      <c r="J29" s="7">
+        <v>75.8</v>
       </c>
       <c r="K29" s="5">
         <v>12.0</v>
@@ -3161,13 +3161,13 @@
       <c r="X29" s="5">
         <v>4.1</v>
       </c>
-      <c r="Y29" s="8">
+      <c r="Y29" s="7">
         <v>100.6</v>
       </c>
-      <c r="Z29" s="8">
+      <c r="Z29" s="7">
         <v>41.0</v>
       </c>
-      <c r="AA29" s="7">
+      <c r="AA29" s="8">
         <v>25.8</v>
       </c>
       <c r="AB29" s="6"/>
@@ -3198,8 +3198,8 @@
         <v>333.9</v>
       </c>
       <c r="I30" s="6"/>
-      <c r="J30" s="8">
-        <v>96.6</v>
+      <c r="J30" s="7">
+        <v>75.7</v>
       </c>
       <c r="K30" s="5">
         <v>12.0</v>
@@ -3244,13 +3244,13 @@
       <c r="X30" s="5">
         <v>5.4</v>
       </c>
-      <c r="Y30" s="8">
+      <c r="Y30" s="7">
         <v>88.5</v>
       </c>
-      <c r="Z30" s="8">
+      <c r="Z30" s="7">
         <v>60.8</v>
       </c>
-      <c r="AA30" s="7">
+      <c r="AA30" s="8">
         <v>25.8</v>
       </c>
       <c r="AB30" s="6"/>
@@ -3281,8 +3281,8 @@
         <v>333.9</v>
       </c>
       <c r="I31" s="6"/>
-      <c r="J31" s="8">
-        <v>95.2</v>
+      <c r="J31" s="7">
+        <v>74.6</v>
       </c>
       <c r="K31" s="5">
         <v>12.0</v>
@@ -3328,13 +3328,13 @@
       <c r="X31" s="5">
         <v>6.8</v>
       </c>
-      <c r="Y31" s="8">
+      <c r="Y31" s="7">
         <v>75.6</v>
       </c>
-      <c r="Z31" s="8">
+      <c r="Z31" s="7">
         <v>90.3</v>
       </c>
-      <c r="AA31" s="7">
+      <c r="AA31" s="8">
         <v>25.4</v>
       </c>
       <c r="AB31" s="6"/>
@@ -3365,8 +3365,8 @@
         <v>333.9</v>
       </c>
       <c r="I32" s="6"/>
-      <c r="J32" s="8">
-        <v>93.6</v>
+      <c r="J32" s="7">
+        <v>73.4</v>
       </c>
       <c r="K32" s="5">
         <v>12.0</v>
@@ -3412,13 +3412,13 @@
       <c r="X32" s="5">
         <v>8.3</v>
       </c>
-      <c r="Y32" s="8">
+      <c r="Y32" s="7">
         <v>67.1</v>
       </c>
-      <c r="Z32" s="8">
+      <c r="Z32" s="7">
         <v>123.6</v>
       </c>
-      <c r="AA32" s="7">
+      <c r="AA32" s="8">
         <v>24.9</v>
       </c>
       <c r="AB32" s="6"/>
@@ -3449,8 +3449,8 @@
         <v>333.9</v>
       </c>
       <c r="I33" s="6"/>
-      <c r="J33" s="8">
-        <v>80.5</v>
+      <c r="J33" s="7">
+        <v>63.4</v>
       </c>
       <c r="K33" s="5">
         <v>12.0</v>
@@ -3496,13 +3496,13 @@
       <c r="X33" s="5">
         <v>4.1</v>
       </c>
-      <c r="Y33" s="8">
+      <c r="Y33" s="7">
         <v>103.2</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="Z33" s="7">
         <v>39.6</v>
       </c>
-      <c r="AA33" s="7">
+      <c r="AA33" s="8">
         <v>20.9</v>
       </c>
       <c r="AB33" s="6"/>
@@ -3533,8 +3533,8 @@
         <v>333.9</v>
       </c>
       <c r="I34" s="6"/>
-      <c r="J34" s="8">
-        <v>78.6</v>
+      <c r="J34" s="7">
+        <v>62.0</v>
       </c>
       <c r="K34" s="5">
         <v>12.0</v>
@@ -3580,13 +3580,13 @@
       <c r="X34" s="5">
         <v>5.4</v>
       </c>
-      <c r="Y34" s="8">
+      <c r="Y34" s="7">
         <v>93.3</v>
       </c>
-      <c r="Z34" s="8">
+      <c r="Z34" s="7">
         <v>58.4</v>
       </c>
-      <c r="AA34" s="7">
+      <c r="AA34" s="8">
         <v>20.3</v>
       </c>
       <c r="AB34" s="6"/>
@@ -3617,8 +3617,8 @@
         <v>333.9</v>
       </c>
       <c r="I35" s="6"/>
-      <c r="J35" s="8">
-        <v>76.9</v>
+      <c r="J35" s="7">
+        <v>60.7</v>
       </c>
       <c r="K35" s="5">
         <v>12.0</v>
@@ -3664,13 +3664,13 @@
       <c r="X35" s="5">
         <v>6.9</v>
       </c>
-      <c r="Y35" s="8">
+      <c r="Y35" s="7">
         <v>83.9</v>
       </c>
-      <c r="Z35" s="8">
+      <c r="Z35" s="7">
         <v>82.2</v>
       </c>
-      <c r="AA35" s="7">
+      <c r="AA35" s="8">
         <v>19.8</v>
       </c>
       <c r="AB35" s="6"/>
@@ -3701,8 +3701,8 @@
         <v>333.9</v>
       </c>
       <c r="I36" s="6"/>
-      <c r="J36" s="8">
-        <v>117.0</v>
+      <c r="J36" s="7">
+        <v>72.1</v>
       </c>
       <c r="K36" s="5">
         <v>27.4</v>
@@ -3748,13 +3748,13 @@
       <c r="X36" s="5">
         <v>5.4</v>
       </c>
-      <c r="Y36" s="8">
+      <c r="Y36" s="7">
         <v>85.2</v>
       </c>
-      <c r="Z36" s="8">
+      <c r="Z36" s="7">
         <v>63.3</v>
       </c>
-      <c r="AA36" s="7">
+      <c r="AA36" s="8">
         <v>24.2</v>
       </c>
       <c r="AB36" s="4" t="s">
@@ -3787,8 +3787,8 @@
         <v>333.9</v>
       </c>
       <c r="I37" s="6"/>
-      <c r="J37" s="5">
-        <v>94.3</v>
+      <c r="J37" s="7">
+        <v>58.7</v>
       </c>
       <c r="K37" s="5">
         <v>27.4</v>
@@ -3840,7 +3840,7 @@
       <c r="Z37" s="5">
         <v>37.3</v>
       </c>
-      <c r="AA37" s="7">
+      <c r="AA37" s="8">
         <v>18.9</v>
       </c>
       <c r="AB37" s="4" t="s">
@@ -3873,8 +3873,8 @@
         <v>333.9</v>
       </c>
       <c r="I38" s="6"/>
-      <c r="J38" s="5">
-        <v>93.6</v>
+      <c r="J38" s="7">
+        <v>58.2</v>
       </c>
       <c r="K38" s="5">
         <v>27.4</v>
@@ -3926,7 +3926,7 @@
       <c r="Z38" s="5">
         <v>55.8</v>
       </c>
-      <c r="AA38" s="7">
+      <c r="AA38" s="8">
         <v>18.8</v>
       </c>
       <c r="AB38" s="6"/>
@@ -3957,8 +3957,8 @@
         <v>333.9</v>
       </c>
       <c r="I39" s="6"/>
-      <c r="J39" s="8">
-        <v>92.9</v>
+      <c r="J39" s="7">
+        <v>57.8</v>
       </c>
       <c r="K39" s="5">
         <v>27.4</v>
@@ -4010,7 +4010,7 @@
       <c r="Z39" s="5">
         <v>80.7</v>
       </c>
-      <c r="AA39" s="7">
+      <c r="AA39" s="8">
         <v>18.6</v>
       </c>
       <c r="AB39" s="4" t="s">
@@ -4043,8 +4043,8 @@
         <v>333.9</v>
       </c>
       <c r="I40" s="6"/>
-      <c r="J40" s="5">
-        <v>118.8</v>
+      <c r="J40" s="7">
+        <v>73.1</v>
       </c>
       <c r="K40" s="5">
         <v>27.4</v>
@@ -4096,7 +4096,7 @@
       <c r="Z40" s="5">
         <v>25.3</v>
       </c>
-      <c r="AA40" s="7">
+      <c r="AA40" s="8">
         <v>24.6</v>
       </c>
       <c r="AB40" s="6"/>
@@ -4127,8 +4127,8 @@
         <v>333.9</v>
       </c>
       <c r="I41" s="6"/>
-      <c r="J41" s="5">
-        <v>118.7</v>
+      <c r="J41" s="7">
+        <v>73.1</v>
       </c>
       <c r="K41" s="5">
         <v>27.4</v>
@@ -4180,7 +4180,7 @@
       <c r="Z41" s="5">
         <v>40.9</v>
       </c>
-      <c r="AA41" s="7">
+      <c r="AA41" s="8">
         <v>24.6</v>
       </c>
       <c r="AB41" s="6"/>
@@ -4211,8 +4211,8 @@
         <v>333.9</v>
       </c>
       <c r="I42" s="6"/>
-      <c r="J42" s="5">
-        <v>118.1</v>
+      <c r="J42" s="7">
+        <v>72.6</v>
       </c>
       <c r="K42" s="5">
         <v>27.4</v>
@@ -4264,7 +4264,7 @@
       <c r="Z42" s="5">
         <v>61.8</v>
       </c>
-      <c r="AA42" s="7">
+      <c r="AA42" s="8">
         <v>24.5</v>
       </c>
       <c r="AB42" s="6"/>
@@ -4295,8 +4295,8 @@
         <v>333.9</v>
       </c>
       <c r="I43" s="6"/>
-      <c r="J43" s="5">
-        <v>117.1</v>
+      <c r="J43" s="7">
+        <v>72.1</v>
       </c>
       <c r="K43" s="5">
         <v>27.4</v>
@@ -4348,7 +4348,7 @@
       <c r="Z43" s="5">
         <v>91.0</v>
       </c>
-      <c r="AA43" s="7">
+      <c r="AA43" s="8">
         <v>24.2</v>
       </c>
       <c r="AB43" s="6"/>
@@ -4379,8 +4379,8 @@
         <v>333.9</v>
       </c>
       <c r="I44" s="6"/>
-      <c r="J44" s="5">
-        <v>116.2</v>
+      <c r="J44" s="7">
+        <v>71.6</v>
       </c>
       <c r="K44" s="5">
         <v>27.4</v>
@@ -4432,7 +4432,7 @@
       <c r="Z44" s="5">
         <v>123.3</v>
       </c>
-      <c r="AA44" s="7">
+      <c r="AA44" s="8">
         <v>24.0</v>
       </c>
       <c r="AB44" s="6"/>
@@ -4463,8 +4463,8 @@
         <v>333.9</v>
       </c>
       <c r="I45" s="6"/>
-      <c r="J45" s="5">
-        <v>117.5</v>
+      <c r="J45" s="7">
+        <v>91.6</v>
       </c>
       <c r="K45" s="5">
         <v>12.0</v>
@@ -4516,7 +4516,7 @@
       <c r="Z45" s="5">
         <v>27.5</v>
       </c>
-      <c r="AA45" s="7">
+      <c r="AA45" s="8">
         <v>32.6</v>
       </c>
       <c r="AB45" s="4" t="s">
@@ -4549,8 +4549,8 @@
         <v>333.9</v>
       </c>
       <c r="I46" s="6"/>
-      <c r="J46" s="5">
-        <v>116.9</v>
+      <c r="J46" s="7">
+        <v>91.1</v>
       </c>
       <c r="K46" s="5">
         <v>12.0</v>
@@ -4602,7 +4602,7 @@
       <c r="Z46" s="5">
         <v>45.4</v>
       </c>
-      <c r="AA46" s="7">
+      <c r="AA46" s="8">
         <v>32.5</v>
       </c>
       <c r="AB46" s="6"/>
@@ -4633,8 +4633,8 @@
         <v>333.9</v>
       </c>
       <c r="I47" s="6"/>
-      <c r="J47" s="5">
-        <v>116.0</v>
+      <c r="J47" s="7">
+        <v>90.5</v>
       </c>
       <c r="K47" s="5">
         <v>12.0</v>
@@ -4686,7 +4686,7 @@
       <c r="Z47" s="5">
         <v>66.8</v>
       </c>
-      <c r="AA47" s="7">
+      <c r="AA47" s="8">
         <v>32.2</v>
       </c>
       <c r="AB47" s="6"/>
@@ -4717,8 +4717,8 @@
         <v>333.9</v>
       </c>
       <c r="I48" s="6"/>
-      <c r="J48" s="5">
-        <v>116.0</v>
+      <c r="J48" s="7">
+        <v>90.4</v>
       </c>
       <c r="K48" s="5">
         <v>12.0</v>
@@ -4770,7 +4770,7 @@
       <c r="Z48" s="5">
         <v>97.1</v>
       </c>
-      <c r="AA48" s="7">
+      <c r="AA48" s="8">
         <v>32.2</v>
       </c>
       <c r="AB48" s="6"/>
@@ -4801,8 +4801,8 @@
         <v>333.9</v>
       </c>
       <c r="I49" s="6"/>
-      <c r="J49" s="5">
-        <v>115.1</v>
+      <c r="J49" s="7">
+        <v>89.8</v>
       </c>
       <c r="K49" s="5">
         <v>12.0</v>
@@ -4854,7 +4854,7 @@
       <c r="Z49" s="5">
         <v>131.6</v>
       </c>
-      <c r="AA49" s="7">
+      <c r="AA49" s="8">
         <v>31.8</v>
       </c>
       <c r="AB49" s="6"/>
@@ -4885,8 +4885,8 @@
         <v>333.9</v>
       </c>
       <c r="I50" s="6"/>
-      <c r="J50" s="5">
-        <v>99.4</v>
+      <c r="J50" s="7">
+        <v>77.5</v>
       </c>
       <c r="K50" s="5">
         <v>12.0</v>
@@ -4938,7 +4938,7 @@
       <c r="Z50" s="5">
         <v>27.2</v>
       </c>
-      <c r="AA50" s="7">
+      <c r="AA50" s="8">
         <v>26.8</v>
       </c>
       <c r="AB50" s="4" t="s">
@@ -4971,8 +4971,8 @@
         <v>333.9</v>
       </c>
       <c r="I51" s="6"/>
-      <c r="J51" s="5">
-        <v>97.4</v>
+      <c r="J51" s="7">
+        <v>76.0</v>
       </c>
       <c r="K51" s="5">
         <v>12.0</v>
@@ -5024,7 +5024,7 @@
       <c r="Z51" s="5">
         <v>64.5</v>
       </c>
-      <c r="AA51" s="7">
+      <c r="AA51" s="8">
         <v>26.1</v>
       </c>
       <c r="AB51" s="4" t="s">
@@ -5057,8 +5057,8 @@
         <v>333.9</v>
       </c>
       <c r="I52" s="6"/>
-      <c r="J52" s="5">
-        <v>95.8</v>
+      <c r="J52" s="7">
+        <v>74.8</v>
       </c>
       <c r="K52" s="5">
         <v>12.0</v>
@@ -5110,7 +5110,7 @@
       <c r="Z52" s="5">
         <v>122.7</v>
       </c>
-      <c r="AA52" s="7">
+      <c r="AA52" s="8">
         <v>25.6</v>
       </c>
       <c r="AB52" s="4" t="s">
@@ -5143,8 +5143,8 @@
         <v>333.9</v>
       </c>
       <c r="I53" s="6"/>
-      <c r="J53" s="5">
-        <v>111.8</v>
+      <c r="J53" s="7">
+        <v>87.1</v>
       </c>
       <c r="K53" s="5">
         <v>12.0</v>
@@ -5196,7 +5196,7 @@
       <c r="Z53" s="5">
         <v>29.9</v>
       </c>
-      <c r="AA53" s="7">
+      <c r="AA53" s="8">
         <v>30.5</v>
       </c>
       <c r="AB53" s="4" t="s">
@@ -5229,8 +5229,8 @@
         <v>333.9</v>
       </c>
       <c r="I54" s="6"/>
-      <c r="J54" s="5">
-        <v>112.2</v>
+      <c r="J54" s="7">
+        <v>87.3</v>
       </c>
       <c r="K54" s="5">
         <v>12.0</v>
@@ -5282,7 +5282,7 @@
       <c r="Z54" s="5">
         <v>70.5</v>
       </c>
-      <c r="AA54" s="7">
+      <c r="AA54" s="8">
         <v>30.8</v>
       </c>
       <c r="AB54" s="4" t="s">
@@ -5315,8 +5315,8 @@
         <v>333.9</v>
       </c>
       <c r="I55" s="6"/>
-      <c r="J55" s="5">
-        <v>112.1</v>
+      <c r="J55" s="7">
+        <v>87.3</v>
       </c>
       <c r="K55" s="5">
         <v>12.0</v>
@@ -5368,7 +5368,7 @@
       <c r="Z55" s="5">
         <v>135.9</v>
       </c>
-      <c r="AA55" s="7">
+      <c r="AA55" s="8">
         <v>30.7</v>
       </c>
       <c r="AB55" s="4" t="s">
@@ -5401,8 +5401,8 @@
         <v>333.9</v>
       </c>
       <c r="I56" s="6"/>
-      <c r="J56" s="5">
-        <v>118.2</v>
+      <c r="J56" s="7">
+        <v>72.6</v>
       </c>
       <c r="K56" s="5">
         <v>27.4</v>
@@ -5454,7 +5454,7 @@
       <c r="Z56" s="5">
         <v>66.8</v>
       </c>
-      <c r="AA56" s="7">
+      <c r="AA56" s="8">
         <v>24.4</v>
       </c>
       <c r="AB56" s="4" t="s">
@@ -5487,8 +5487,8 @@
         <v>337.7</v>
       </c>
       <c r="I57" s="6"/>
-      <c r="J57" s="5">
-        <v>113.9</v>
+      <c r="J57" s="7">
+        <v>99.3</v>
       </c>
       <c r="K57" s="5">
         <v>6.0</v>
@@ -5540,7 +5540,7 @@
       <c r="Z57" s="5">
         <v>50.9</v>
       </c>
-      <c r="AA57" s="7">
+      <c r="AA57" s="8">
         <v>35.8</v>
       </c>
       <c r="AB57" s="4" t="s">
@@ -5573,8 +5573,8 @@
         <v>337.7</v>
       </c>
       <c r="I58" s="6"/>
-      <c r="J58" s="5">
-        <v>113.9</v>
+      <c r="J58" s="7">
+        <v>99.3</v>
       </c>
       <c r="K58" s="5">
         <v>6.0</v>
@@ -5626,7 +5626,7 @@
       <c r="Z58" s="5">
         <v>76.2</v>
       </c>
-      <c r="AA58" s="7">
+      <c r="AA58" s="8">
         <v>35.9</v>
       </c>
       <c r="AB58" s="6"/>
@@ -5657,8 +5657,8 @@
         <v>337.7</v>
       </c>
       <c r="I59" s="6"/>
-      <c r="J59" s="5">
-        <v>113.8</v>
+      <c r="J59" s="7">
+        <v>99.2</v>
       </c>
       <c r="K59" s="5">
         <v>6.0</v>
@@ -5710,7 +5710,7 @@
       <c r="Z59" s="5">
         <v>116.1</v>
       </c>
-      <c r="AA59" s="7">
+      <c r="AA59" s="8">
         <v>35.8</v>
       </c>
       <c r="AB59" s="6"/>
@@ -5741,8 +5741,8 @@
         <v>337.7</v>
       </c>
       <c r="I60" s="6"/>
-      <c r="J60" s="5">
-        <v>98.8</v>
+      <c r="J60" s="7">
+        <v>86.3</v>
       </c>
       <c r="K60" s="5">
         <v>6.0</v>
@@ -5794,7 +5794,7 @@
       <c r="Z60" s="5">
         <v>27.4</v>
       </c>
-      <c r="AA60" s="7">
+      <c r="AA60" s="8">
         <v>30.1</v>
       </c>
       <c r="AB60" s="6"/>
@@ -5825,8 +5825,8 @@
         <v>337.7</v>
       </c>
       <c r="I61" s="6"/>
-      <c r="J61" s="5">
-        <v>97.4</v>
+      <c r="J61" s="7">
+        <v>85.1</v>
       </c>
       <c r="K61" s="5">
         <v>6.0</v>
@@ -5878,7 +5878,7 @@
       <c r="Z61" s="5">
         <v>46.0</v>
       </c>
-      <c r="AA61" s="7">
+      <c r="AA61" s="8">
         <v>29.6</v>
       </c>
       <c r="AB61" s="6"/>
@@ -5909,8 +5909,8 @@
         <v>337.7</v>
       </c>
       <c r="I62" s="6"/>
-      <c r="J62" s="5">
-        <v>97.2</v>
+      <c r="J62" s="7">
+        <v>84.9</v>
       </c>
       <c r="K62" s="5">
         <v>6.0</v>
@@ -5962,7 +5962,7 @@
       <c r="Z62" s="5">
         <v>69.8</v>
       </c>
-      <c r="AA62" s="7">
+      <c r="AA62" s="8">
         <v>29.5</v>
       </c>
       <c r="AB62" s="6"/>
@@ -5993,8 +5993,8 @@
         <v>337.7</v>
       </c>
       <c r="I63" s="6"/>
-      <c r="J63" s="5">
-        <v>96.6</v>
+      <c r="J63" s="7">
+        <v>84.4</v>
       </c>
       <c r="K63" s="5">
         <v>6.0</v>
@@ -6046,7 +6046,7 @@
       <c r="Z63" s="5">
         <v>119.7</v>
       </c>
-      <c r="AA63" s="7">
+      <c r="AA63" s="8">
         <v>29.4</v>
       </c>
       <c r="AB63" s="6"/>
@@ -6077,8 +6077,8 @@
         <v>337.7</v>
       </c>
       <c r="I64" s="6"/>
-      <c r="J64" s="5">
-        <v>96.5</v>
+      <c r="J64" s="7">
+        <v>84.3</v>
       </c>
       <c r="K64" s="5">
         <v>6.0</v>
@@ -6130,7 +6130,7 @@
       <c r="Z64" s="5">
         <v>145.0</v>
       </c>
-      <c r="AA64" s="7">
+      <c r="AA64" s="8">
         <v>29.3</v>
       </c>
       <c r="AB64" s="6"/>
@@ -6161,8 +6161,8 @@
         <v>337.7</v>
       </c>
       <c r="I65" s="6"/>
-      <c r="J65" s="5">
-        <v>110.2</v>
+      <c r="J65" s="7">
+        <v>68.1</v>
       </c>
       <c r="K65" s="5">
         <v>27.4</v>
@@ -6214,7 +6214,7 @@
       <c r="Z65" s="5">
         <v>25.9</v>
       </c>
-      <c r="AA65" s="7">
+      <c r="AA65" s="8">
         <v>22.4</v>
       </c>
       <c r="AB65" s="4" t="s">
@@ -6247,8 +6247,8 @@
         <v>337.7</v>
       </c>
       <c r="I66" s="6"/>
-      <c r="J66" s="5">
-        <v>109.5</v>
+      <c r="J66" s="7">
+        <v>67.7</v>
       </c>
       <c r="K66" s="5">
         <v>27.4</v>
@@ -6300,7 +6300,7 @@
       <c r="Z66" s="5">
         <v>42.6</v>
       </c>
-      <c r="AA66" s="7">
+      <c r="AA66" s="8">
         <v>22.2</v>
       </c>
       <c r="AB66" s="6"/>
@@ -6331,8 +6331,8 @@
         <v>337.7</v>
       </c>
       <c r="I67" s="6"/>
-      <c r="J67" s="5">
-        <v>108.8</v>
+      <c r="J67" s="7">
+        <v>67.2</v>
       </c>
       <c r="K67" s="5">
         <v>27.4</v>
@@ -6384,7 +6384,7 @@
       <c r="Z67" s="5">
         <v>65.9</v>
       </c>
-      <c r="AA67" s="7">
+      <c r="AA67" s="8">
         <v>22.1</v>
       </c>
       <c r="AB67" s="6"/>
@@ -6415,8 +6415,8 @@
         <v>337.7</v>
       </c>
       <c r="I68" s="6"/>
-      <c r="J68" s="5">
-        <v>107.8</v>
+      <c r="J68" s="7">
+        <v>66.7</v>
       </c>
       <c r="K68" s="5">
         <v>27.4</v>
@@ -6468,7 +6468,7 @@
       <c r="Z68" s="5">
         <v>96.8</v>
       </c>
-      <c r="AA68" s="7">
+      <c r="AA68" s="8">
         <v>21.8</v>
       </c>
       <c r="AB68" s="6"/>
@@ -6499,8 +6499,8 @@
         <v>337.7</v>
       </c>
       <c r="I69" s="6"/>
-      <c r="J69" s="5">
-        <v>107.7</v>
+      <c r="J69" s="7">
+        <v>66.7</v>
       </c>
       <c r="K69" s="5">
         <v>27.4</v>
@@ -6552,7 +6552,7 @@
       <c r="Z69" s="5">
         <v>136.0</v>
       </c>
-      <c r="AA69" s="7">
+      <c r="AA69" s="8">
         <v>21.8</v>
       </c>
       <c r="AB69" s="6"/>
@@ -6583,8 +6583,8 @@
         <v>337.7</v>
       </c>
       <c r="I70" s="6"/>
-      <c r="J70" s="5">
-        <v>89.1</v>
+      <c r="J70" s="7">
+        <v>55.7</v>
       </c>
       <c r="K70" s="5">
         <v>27.4</v>
@@ -6636,7 +6636,7 @@
       <c r="Z70" s="5">
         <v>41.2</v>
       </c>
-      <c r="AA70" s="7">
+      <c r="AA70" s="8">
         <v>17.6</v>
       </c>
       <c r="AB70" s="4" t="s">
@@ -6669,8 +6669,8 @@
         <v>337.7</v>
       </c>
       <c r="I71" s="6"/>
-      <c r="J71" s="5">
-        <v>88.4</v>
+      <c r="J71" s="7">
+        <v>55.3</v>
       </c>
       <c r="K71" s="5">
         <v>27.4</v>
@@ -6722,7 +6722,7 @@
       <c r="Z71" s="5">
         <v>61.1</v>
       </c>
-      <c r="AA71" s="7">
+      <c r="AA71" s="8">
         <v>17.4</v>
       </c>
       <c r="AB71" s="6"/>
@@ -6753,8 +6753,8 @@
         <v>337.7</v>
       </c>
       <c r="I72" s="6"/>
-      <c r="J72" s="5">
-        <v>87.4</v>
+      <c r="J72" s="7">
+        <v>54.8</v>
       </c>
       <c r="K72" s="5">
         <v>27.4</v>
@@ -6806,7 +6806,7 @@
       <c r="Z72" s="5">
         <v>88.0</v>
       </c>
-      <c r="AA72" s="7">
+      <c r="AA72" s="8">
         <v>17.2</v>
       </c>
       <c r="AB72" s="6"/>
@@ -6837,8 +6837,8 @@
         <v>337.7</v>
       </c>
       <c r="I73" s="6"/>
-      <c r="J73" s="5">
-        <v>111.7</v>
+      <c r="J73" s="7">
+        <v>69.1</v>
       </c>
       <c r="K73" s="5">
         <v>27.4</v>
@@ -6890,7 +6890,7 @@
       <c r="Z73" s="5">
         <v>58.7</v>
       </c>
-      <c r="AA73" s="7">
+      <c r="AA73" s="8">
         <v>22.7</v>
       </c>
       <c r="AB73" s="4" t="s">
@@ -6923,8 +6923,8 @@
         <v>337.7</v>
       </c>
       <c r="I74" s="6"/>
-      <c r="J74" s="5">
-        <v>111.9</v>
+      <c r="J74" s="7">
+        <v>69.1</v>
       </c>
       <c r="K74" s="5">
         <v>27.4</v>
@@ -6976,7 +6976,7 @@
       <c r="Z74" s="5">
         <v>58.9</v>
       </c>
-      <c r="AA74" s="7">
+      <c r="AA74" s="8">
         <v>22.8</v>
       </c>
       <c r="AB74" s="4" t="s">
@@ -7009,8 +7009,8 @@
         <v>337.7</v>
       </c>
       <c r="I75" s="6"/>
-      <c r="J75" s="5">
-        <v>111.7</v>
+      <c r="J75" s="7">
+        <v>69.1</v>
       </c>
       <c r="K75" s="5">
         <v>27.4</v>
@@ -7062,7 +7062,7 @@
       <c r="Z75" s="5">
         <v>24.4</v>
       </c>
-      <c r="AA75" s="7">
+      <c r="AA75" s="8">
         <v>22.7</v>
       </c>
       <c r="AB75" s="6"/>
@@ -7093,8 +7093,8 @@
         <v>337.7</v>
       </c>
       <c r="I76" s="6"/>
-      <c r="J76" s="5">
-        <v>111.0</v>
+      <c r="J76" s="7">
+        <v>68.6</v>
       </c>
       <c r="K76" s="5">
         <v>27.4</v>
@@ -7146,7 +7146,7 @@
       <c r="Z76" s="5">
         <v>120.4</v>
       </c>
-      <c r="AA76" s="7">
+      <c r="AA76" s="8">
         <v>22.5</v>
       </c>
       <c r="AB76" s="6"/>
@@ -7177,8 +7177,8 @@
         <v>333.9</v>
       </c>
       <c r="I77" s="6"/>
-      <c r="J77" s="5">
-        <v>118.4</v>
+      <c r="J77" s="7">
+        <v>72.6</v>
       </c>
       <c r="K77" s="5">
         <v>27.4</v>
@@ -7230,7 +7230,7 @@
       <c r="Z77" s="5">
         <v>59.9</v>
       </c>
-      <c r="AA77" s="7">
+      <c r="AA77" s="8">
         <v>24.4</v>
       </c>
       <c r="AB77" s="4" t="s">
@@ -7263,8 +7263,8 @@
         <v>333.9</v>
       </c>
       <c r="I78" s="6"/>
-      <c r="J78" s="5">
-        <v>118.0</v>
+      <c r="J78" s="7">
+        <v>72.5</v>
       </c>
       <c r="K78" s="5">
         <v>27.4</v>
@@ -7316,7 +7316,7 @@
       <c r="Z78" s="5">
         <v>24.2</v>
       </c>
-      <c r="AA78" s="7">
+      <c r="AA78" s="8">
         <v>24.3</v>
       </c>
       <c r="AB78" s="6"/>
@@ -7347,8 +7347,8 @@
         <v>333.9</v>
       </c>
       <c r="I79" s="6"/>
-      <c r="J79" s="5">
-        <v>117.3</v>
+      <c r="J79" s="7">
+        <v>72.1</v>
       </c>
       <c r="K79" s="5">
         <v>27.4</v>
@@ -7400,7 +7400,7 @@
       <c r="Z79" s="5">
         <v>112.7</v>
       </c>
-      <c r="AA79" s="7">
+      <c r="AA79" s="8">
         <v>24.1</v>
       </c>
       <c r="AB79" s="4" t="s">
@@ -7433,10 +7433,10 @@
         <v>333.9</v>
       </c>
       <c r="I80" s="6"/>
-      <c r="J80" s="5">
-        <v>71.4</v>
-      </c>
-      <c r="K80" s="8">
+      <c r="J80" s="7">
+        <v>73.2</v>
+      </c>
+      <c r="K80" s="7">
         <v>29.3</v>
       </c>
       <c r="L80" s="4">
@@ -7478,7 +7478,7 @@
         <v>125.3</v>
       </c>
       <c r="Z80" s="5"/>
-      <c r="AA80" s="8">
+      <c r="AA80" s="7">
         <v>25.3</v>
       </c>
       <c r="AB80" s="4" t="s">
@@ -7511,10 +7511,10 @@
         <v>333.9</v>
       </c>
       <c r="I81" s="6"/>
-      <c r="J81" s="5">
-        <v>73.0</v>
-      </c>
-      <c r="K81" s="8">
+      <c r="J81" s="7">
+        <v>74.2</v>
+      </c>
+      <c r="K81" s="7">
         <v>29.3</v>
       </c>
       <c r="L81" s="4">
@@ -7556,7 +7556,7 @@
         <v>101.5</v>
       </c>
       <c r="Z81" s="5"/>
-      <c r="AA81" s="7">
+      <c r="AA81" s="8">
         <v>25.7</v>
       </c>
       <c r="AB81" s="6"/>
@@ -7574,7 +7574,7 @@
       <c r="D82" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="7">
         <v>26.1</v>
       </c>
       <c r="F82" s="4" t="s">
@@ -7587,10 +7587,10 @@
         <v>333.9</v>
       </c>
       <c r="I82" s="6"/>
-      <c r="J82" s="5">
-        <v>71.3</v>
-      </c>
-      <c r="K82" s="8">
+      <c r="J82" s="7">
+        <v>73.2</v>
+      </c>
+      <c r="K82" s="7">
         <v>29.3</v>
       </c>
       <c r="L82" s="4">
@@ -7632,7 +7632,7 @@
         <v>86.5</v>
       </c>
       <c r="Z82" s="5"/>
-      <c r="AA82" s="8">
+      <c r="AA82" s="7">
         <v>25.3</v>
       </c>
       <c r="AB82" s="6"/>
@@ -7650,7 +7650,7 @@
       <c r="D83" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="7">
         <v>26.1</v>
       </c>
       <c r="F83" s="4" t="s">
@@ -7663,10 +7663,10 @@
         <v>333.9</v>
       </c>
       <c r="I83" s="6"/>
-      <c r="J83" s="5">
-        <v>83.5</v>
-      </c>
-      <c r="K83" s="8">
+      <c r="J83" s="7">
+        <v>85.7</v>
+      </c>
+      <c r="K83" s="7">
         <v>29.3</v>
       </c>
       <c r="L83" s="4">
@@ -7708,7 +7708,7 @@
         <v>122.9</v>
       </c>
       <c r="Z83" s="5"/>
-      <c r="AA83" s="8">
+      <c r="AA83" s="7">
         <v>30.5</v>
       </c>
       <c r="AB83" s="6"/>
@@ -7726,7 +7726,7 @@
       <c r="D84" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="7">
         <v>26.1</v>
       </c>
       <c r="F84" s="4" t="s">
@@ -7739,10 +7739,10 @@
         <v>333.9</v>
       </c>
       <c r="I84" s="6"/>
-      <c r="J84" s="5">
-        <v>82.9</v>
-      </c>
-      <c r="K84" s="8">
+      <c r="J84" s="7">
+        <v>85.0</v>
+      </c>
+      <c r="K84" s="7">
         <v>29.3</v>
       </c>
       <c r="L84" s="4">
@@ -7784,7 +7784,7 @@
         <v>98.9</v>
       </c>
       <c r="Z84" s="5"/>
-      <c r="AA84" s="8">
+      <c r="AA84" s="7">
         <v>30.3</v>
       </c>
       <c r="AB84" s="6"/>
@@ -7802,7 +7802,7 @@
       <c r="D85" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="7">
         <v>26.1</v>
       </c>
       <c r="F85" s="4" t="s">
@@ -7815,10 +7815,10 @@
         <v>333.9</v>
       </c>
       <c r="I85" s="6"/>
-      <c r="J85" s="5">
-        <v>83.8</v>
-      </c>
-      <c r="K85" s="8">
+      <c r="J85" s="7">
+        <v>86.0</v>
+      </c>
+      <c r="K85" s="7">
         <v>29.3</v>
       </c>
       <c r="L85" s="4">
@@ -7860,7 +7860,7 @@
         <v>83.5</v>
       </c>
       <c r="Z85" s="5"/>
-      <c r="AA85" s="8">
+      <c r="AA85" s="7">
         <v>30.8</v>
       </c>
       <c r="AB85" s="6"/>
@@ -7891,10 +7891,10 @@
         <v>337.7</v>
       </c>
       <c r="I86" s="6"/>
-      <c r="J86" s="5">
-        <v>69.6</v>
-      </c>
-      <c r="K86" s="8">
+      <c r="J86" s="7">
+        <v>70.6</v>
+      </c>
+      <c r="K86" s="7">
         <v>29.3</v>
       </c>
       <c r="L86" s="4">
@@ -7936,7 +7936,7 @@
         <v>126.2</v>
       </c>
       <c r="Z86" s="5"/>
-      <c r="AA86" s="7">
+      <c r="AA86" s="8">
         <v>24.0</v>
       </c>
       <c r="AB86" s="6"/>
@@ -7967,10 +7967,10 @@
         <v>337.7</v>
       </c>
       <c r="I87" s="6"/>
-      <c r="J87" s="5">
-        <v>69.6</v>
-      </c>
-      <c r="K87" s="8">
+      <c r="J87" s="7">
+        <v>70.6</v>
+      </c>
+      <c r="K87" s="7">
         <v>29.3</v>
       </c>
       <c r="L87" s="4">
@@ -8012,7 +8012,7 @@
         <v>100.0</v>
       </c>
       <c r="Z87" s="5"/>
-      <c r="AA87" s="7">
+      <c r="AA87" s="8">
         <v>23.9</v>
       </c>
       <c r="AB87" s="6"/>
@@ -8043,10 +8043,10 @@
         <v>337.7</v>
       </c>
       <c r="I88" s="6"/>
-      <c r="J88" s="5">
-        <v>69.7</v>
-      </c>
-      <c r="K88" s="8">
+      <c r="J88" s="7">
+        <v>70.8</v>
+      </c>
+      <c r="K88" s="7">
         <v>29.3</v>
       </c>
       <c r="L88" s="4">
@@ -8088,7 +8088,7 @@
         <v>80.5</v>
       </c>
       <c r="Z88" s="5"/>
-      <c r="AA88" s="7">
+      <c r="AA88" s="8">
         <v>24.1</v>
       </c>
       <c r="AB88" s="6"/>
@@ -8119,10 +8119,10 @@
         <v>337.7</v>
       </c>
       <c r="I89" s="6"/>
-      <c r="J89" s="5">
-        <v>80.7</v>
-      </c>
-      <c r="K89" s="8">
+      <c r="J89" s="7">
+        <v>82.0</v>
+      </c>
+      <c r="K89" s="7">
         <v>29.3</v>
       </c>
       <c r="L89" s="4">
@@ -8164,7 +8164,7 @@
         <v>126.6</v>
       </c>
       <c r="Z89" s="5"/>
-      <c r="AA89" s="7">
+      <c r="AA89" s="8">
         <v>28.8</v>
       </c>
       <c r="AB89" s="6"/>
@@ -8195,10 +8195,10 @@
         <v>337.7</v>
       </c>
       <c r="I90" s="6"/>
-      <c r="J90" s="5">
-        <v>80.6</v>
-      </c>
-      <c r="K90" s="8">
+      <c r="J90" s="7">
+        <v>81.9</v>
+      </c>
+      <c r="K90" s="7">
         <v>29.3</v>
       </c>
       <c r="L90" s="4">
@@ -8240,7 +8240,7 @@
         <v>96.7</v>
       </c>
       <c r="Z90" s="5"/>
-      <c r="AA90" s="7">
+      <c r="AA90" s="8">
         <v>28.7</v>
       </c>
       <c r="AB90" s="6"/>
@@ -8271,10 +8271,10 @@
         <v>337.7</v>
       </c>
       <c r="I91" s="6"/>
-      <c r="J91" s="5">
-        <v>80.8</v>
-      </c>
-      <c r="K91" s="8">
+      <c r="J91" s="7">
+        <v>82.0</v>
+      </c>
+      <c r="K91" s="7">
         <v>27.4</v>
       </c>
       <c r="L91" s="4">
@@ -8316,7 +8316,7 @@
         <v>79.6</v>
       </c>
       <c r="Z91" s="5"/>
-      <c r="AA91" s="7">
+      <c r="AA91" s="8">
         <v>28.9</v>
       </c>
       <c r="AB91" s="6"/>
@@ -8347,8 +8347,8 @@
         <v>458.3</v>
       </c>
       <c r="I92" s="6"/>
-      <c r="J92" s="5">
-        <v>107.0</v>
+      <c r="J92" s="7">
+        <v>66.2</v>
       </c>
       <c r="K92" s="5">
         <v>27.4</v>
@@ -8400,7 +8400,7 @@
       <c r="Z92" s="5">
         <v>61.4</v>
       </c>
-      <c r="AA92" s="7">
+      <c r="AA92" s="8">
         <v>21.6</v>
       </c>
       <c r="AB92" s="4" t="s">
@@ -8433,8 +8433,8 @@
         <v>458.3</v>
       </c>
       <c r="I93" s="6"/>
-      <c r="J93" s="5">
-        <v>107.8</v>
+      <c r="J93" s="7">
+        <v>66.7</v>
       </c>
       <c r="K93" s="5">
         <v>27.4</v>
@@ -8486,7 +8486,7 @@
       <c r="Z93" s="5">
         <v>59.3</v>
       </c>
-      <c r="AA93" s="7">
+      <c r="AA93" s="8">
         <v>21.8</v>
       </c>
       <c r="AB93" s="4" t="s">
@@ -8519,8 +8519,8 @@
         <v>458.3</v>
       </c>
       <c r="I94" s="6"/>
-      <c r="J94" s="5">
-        <v>110.9</v>
+      <c r="J94" s="7">
+        <v>68.6</v>
       </c>
       <c r="K94" s="5">
         <v>27.4</v>
@@ -8572,7 +8572,7 @@
       <c r="Z94" s="5">
         <v>59.7</v>
       </c>
-      <c r="AA94" s="7">
+      <c r="AA94" s="8">
         <v>22.5</v>
       </c>
       <c r="AB94" s="4" t="s">
@@ -8659,8 +8659,8 @@
         <v>453.2</v>
       </c>
       <c r="I96" s="6"/>
-      <c r="J96" s="5">
-        <v>107.5</v>
+      <c r="J96" s="7">
+        <v>66.3</v>
       </c>
       <c r="K96" s="5">
         <v>27.4</v>
@@ -8712,7 +8712,7 @@
       <c r="Z96" s="5">
         <v>61.4</v>
       </c>
-      <c r="AA96" s="7">
+      <c r="AA96" s="8">
         <v>21.8</v>
       </c>
       <c r="AB96" s="4" t="s">
@@ -8745,8 +8745,8 @@
         <v>453.2</v>
       </c>
       <c r="I97" s="6"/>
-      <c r="J97" s="5">
-        <v>110.5</v>
+      <c r="J97" s="7">
+        <v>68.2</v>
       </c>
       <c r="K97" s="5">
         <v>27.4</v>
@@ -8798,7 +8798,7 @@
       <c r="Z97" s="5">
         <v>60.6</v>
       </c>
-      <c r="AA97" s="7">
+      <c r="AA97" s="8">
         <v>22.5</v>
       </c>
       <c r="AB97" s="4" t="s">
@@ -8831,8 +8831,8 @@
         <v>453.2</v>
       </c>
       <c r="I98" s="6"/>
-      <c r="J98" s="5">
-        <v>113.8</v>
+      <c r="J98" s="7">
+        <v>70.2</v>
       </c>
       <c r="K98" s="5">
         <v>27.4</v>
@@ -8884,7 +8884,7 @@
       <c r="Z98" s="5">
         <v>57.9</v>
       </c>
-      <c r="AA98" s="7">
+      <c r="AA98" s="8">
         <v>23.4</v>
       </c>
       <c r="AB98" s="4" t="s">
@@ -8917,8 +8917,8 @@
         <v>453.2</v>
       </c>
       <c r="I99" s="6"/>
-      <c r="J99" s="5">
-        <v>113.7</v>
+      <c r="J99" s="7">
+        <v>70.2</v>
       </c>
       <c r="K99" s="5">
         <v>27.4</v>
